--- a/results/q4_output/problem4_final_result.xlsx
+++ b/results/q4_output/problem4_final_result.xlsx
@@ -483,10 +483,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17977.70078277588</v>
+        <v>25035.2265625</v>
       </c>
       <c r="F2" t="n">
-        <v>1962.439331054688</v>
+        <v>1781.177001953125</v>
       </c>
     </row>
     <row r="3">
@@ -507,10 +507,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>16926.73729515076</v>
+        <v>23233.1640625</v>
       </c>
       <c r="F3" t="n">
-        <v>2213.71337890625</v>
+        <v>1821.574096679688</v>
       </c>
     </row>
     <row r="4">
@@ -531,10 +531,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>16488.24035525322</v>
+        <v>22607.12109375</v>
       </c>
       <c r="F4" t="n">
-        <v>1951.3349609375</v>
+        <v>2046.7705078125</v>
       </c>
     </row>
     <row r="5">
@@ -555,10 +555,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>16183.32241249084</v>
+        <v>19879.025390625</v>
       </c>
       <c r="F5" t="n">
-        <v>1758.646606445312</v>
+        <v>2044.526977539062</v>
       </c>
     </row>
     <row r="6">
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>15582.0695605278</v>
+        <v>16208.5341796875</v>
       </c>
       <c r="F6" t="n">
-        <v>1783.058837890625</v>
+        <v>1538.9375</v>
       </c>
     </row>
     <row r="7">
@@ -603,10 +603,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15392.66575288773</v>
+        <v>12749.3369140625</v>
       </c>
       <c r="F7" t="n">
-        <v>2008.546997070312</v>
+        <v>840.0941162109375</v>
       </c>
     </row>
     <row r="8">
@@ -627,10 +627,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>12424.57675504684</v>
+        <v>6033.43994140625</v>
       </c>
       <c r="F8" t="n">
-        <v>1540.460083007812</v>
+        <v>554.9016723632812</v>
       </c>
     </row>
     <row r="9">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>9261.790073394775</v>
+        <v>5860.44287109375</v>
       </c>
       <c r="F9" t="n">
-        <v>952.9539794921875</v>
+        <v>848.1298828125</v>
       </c>
     </row>
     <row r="10">
@@ -675,10 +675,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>8220.167894363403</v>
+        <v>1718.232177734375</v>
       </c>
       <c r="F10" t="n">
-        <v>1135.307739257812</v>
+        <v>207.1872711181641</v>
       </c>
     </row>
     <row r="11">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7517.253492355347</v>
+        <v>354.7342529296875</v>
       </c>
       <c r="F11" t="n">
-        <v>894.250244140625</v>
+        <v>68.81431579589844</v>
       </c>
     </row>
     <row r="12">
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>19775.47086105347</v>
+        <v>27538.74921875</v>
       </c>
       <c r="F12" t="n">
-        <v>2158.683264160157</v>
+        <v>1959.294702148438</v>
       </c>
     </row>
     <row r="13">
@@ -747,10 +747,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>18619.41102466584</v>
+        <v>25556.48046875</v>
       </c>
       <c r="F13" t="n">
-        <v>2435.084716796875</v>
+        <v>2003.731506347657</v>
       </c>
     </row>
     <row r="14">
@@ -771,10 +771,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>18137.06439077854</v>
+        <v>24867.833203125</v>
       </c>
       <c r="F14" t="n">
-        <v>2146.46845703125</v>
+        <v>2251.44755859375</v>
       </c>
     </row>
     <row r="15">
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>17801.65465373993</v>
+        <v>21866.9279296875</v>
       </c>
       <c r="F15" t="n">
-        <v>1934.511267089843</v>
+        <v>2248.979675292968</v>
       </c>
     </row>
     <row r="16">
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>17140.27651658058</v>
+        <v>17829.38759765625</v>
       </c>
       <c r="F16" t="n">
-        <v>1961.364721679688</v>
+        <v>1692.83125</v>
       </c>
     </row>
     <row r="17">
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>16931.9323281765</v>
+        <v>14024.27060546875</v>
       </c>
       <c r="F17" t="n">
-        <v>2209.401696777343</v>
+        <v>924.1035278320313</v>
       </c>
     </row>
     <row r="18">
@@ -867,10 +867,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>13667.03443055153</v>
+        <v>6636.783935546876</v>
       </c>
       <c r="F18" t="n">
-        <v>1694.506091308593</v>
+        <v>610.3918395996094</v>
       </c>
     </row>
     <row r="19">
@@ -891,10 +891,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>10187.96908073425</v>
+        <v>6446.487158203126</v>
       </c>
       <c r="F19" t="n">
-        <v>1048.249377441406</v>
+        <v>932.9428710937501</v>
       </c>
     </row>
     <row r="20">
@@ -915,10 +915,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>9042.184683799744</v>
+        <v>1890.055395507813</v>
       </c>
       <c r="F20" t="n">
-        <v>1248.838513183593</v>
+        <v>227.9059982299805</v>
       </c>
     </row>
     <row r="21">
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>8268.978841590882</v>
+        <v>390.2076782226563</v>
       </c>
       <c r="F21" t="n">
-        <v>983.6752685546876</v>
+        <v>75.69574737548828</v>
       </c>
     </row>
     <row r="22">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>21753.01794715882</v>
+        <v>30292.624140625</v>
       </c>
       <c r="F22" t="n">
-        <v>2374.551590576173</v>
+        <v>2155.224172363281</v>
       </c>
     </row>
     <row r="23">
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>20481.35212713242</v>
+        <v>28112.12851562501</v>
       </c>
       <c r="F23" t="n">
-        <v>2678.593188476563</v>
+        <v>2204.104656982423</v>
       </c>
     </row>
     <row r="24">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>19950.7708298564</v>
+        <v>27354.6165234375</v>
       </c>
       <c r="F24" t="n">
-        <v>2361.115302734375</v>
+        <v>2476.592314453125</v>
       </c>
     </row>
     <row r="25">
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>19581.82011911392</v>
+        <v>24053.62072265625</v>
       </c>
       <c r="F25" t="n">
-        <v>2127.962393798828</v>
+        <v>2473.877642822265</v>
       </c>
     </row>
     <row r="26">
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>18854.30416823864</v>
+        <v>19612.32635742188</v>
       </c>
       <c r="F26" t="n">
-        <v>2157.501193847656</v>
+        <v>1862.114375</v>
       </c>
     </row>
     <row r="27">
@@ -1083,10 +1083,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>18625.12556099415</v>
+        <v>15426.69766601563</v>
       </c>
       <c r="F27" t="n">
-        <v>2430.341866455078</v>
+        <v>1016.513880615234</v>
       </c>
     </row>
     <row r="28">
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>15033.73787360668</v>
+        <v>7300.462329101563</v>
       </c>
       <c r="F28" t="n">
-        <v>1863.956700439453</v>
+        <v>671.4310235595705</v>
       </c>
     </row>
     <row r="29">
@@ -1131,10 +1131,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>11206.76598880768</v>
+        <v>7091.135874023438</v>
       </c>
       <c r="F29" t="n">
-        <v>1153.074315185547</v>
+        <v>1026.237158203125</v>
       </c>
     </row>
     <row r="30">
@@ -1155,10 +1155,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>9946.403152179719</v>
+        <v>2079.060935058594</v>
       </c>
       <c r="F30" t="n">
-        <v>1373.722364501953</v>
+        <v>250.6965980529786</v>
       </c>
     </row>
     <row r="31">
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>9095.876725749971</v>
+        <v>429.228446044922</v>
       </c>
       <c r="F31" t="n">
-        <v>1082.042795410156</v>
+        <v>83.26532211303713</v>
       </c>
     </row>
     <row r="32">
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>17977.70078277588</v>
+        <v>25035.2265625</v>
       </c>
       <c r="F32" t="n">
-        <v>1962.439331054688</v>
+        <v>1781.177001953125</v>
       </c>
     </row>
     <row r="33">
@@ -1227,10 +1227,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>16926.73729515076</v>
+        <v>23233.1640625</v>
       </c>
       <c r="F33" t="n">
-        <v>2213.71337890625</v>
+        <v>1821.574096679688</v>
       </c>
     </row>
     <row r="34">
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>16488.24035525322</v>
+        <v>22607.12109375</v>
       </c>
       <c r="F34" t="n">
-        <v>1951.3349609375</v>
+        <v>2046.7705078125</v>
       </c>
     </row>
     <row r="35">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>16183.32241249084</v>
+        <v>19879.025390625</v>
       </c>
       <c r="F35" t="n">
-        <v>1758.646606445312</v>
+        <v>2044.526977539062</v>
       </c>
     </row>
     <row r="36">
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>15582.0695605278</v>
+        <v>16208.5341796875</v>
       </c>
       <c r="F36" t="n">
-        <v>1783.058837890625</v>
+        <v>1538.9375</v>
       </c>
     </row>
     <row r="37">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>15392.66575288773</v>
+        <v>12749.3369140625</v>
       </c>
       <c r="F37" t="n">
-        <v>2008.546997070312</v>
+        <v>840.0941162109375</v>
       </c>
     </row>
     <row r="38">
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>12424.57675504684</v>
+        <v>6033.43994140625</v>
       </c>
       <c r="F38" t="n">
-        <v>1540.460083007812</v>
+        <v>554.9016723632812</v>
       </c>
     </row>
     <row r="39">
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>9261.790073394775</v>
+        <v>5860.44287109375</v>
       </c>
       <c r="F39" t="n">
-        <v>952.9539794921875</v>
+        <v>848.1298828125</v>
       </c>
     </row>
     <row r="40">
@@ -1395,10 +1395,10 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>8220.167894363403</v>
+        <v>1718.232177734375</v>
       </c>
       <c r="F40" t="n">
-        <v>1135.307739257812</v>
+        <v>207.1872711181641</v>
       </c>
     </row>
     <row r="41">
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>7517.253492355347</v>
+        <v>354.7342529296875</v>
       </c>
       <c r="F41" t="n">
-        <v>894.250244140625</v>
+        <v>68.81431579589844</v>
       </c>
     </row>
     <row r="42">
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>20674.35590019226</v>
+        <v>28790.510546875</v>
       </c>
       <c r="F42" t="n">
-        <v>2256.805230712891</v>
+        <v>2048.353552246093</v>
       </c>
     </row>
     <row r="43">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>19465.74788942337</v>
+        <v>26718.138671875</v>
       </c>
       <c r="F43" t="n">
-        <v>2545.770385742188</v>
+        <v>2094.810211181641</v>
       </c>
     </row>
     <row r="44">
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>18961.4764085412</v>
+        <v>25998.1892578125</v>
       </c>
       <c r="F44" t="n">
-        <v>2244.035205078125</v>
+        <v>2353.786083984375</v>
       </c>
     </row>
     <row r="45">
@@ -1515,10 +1515,10 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>18610.82077436446</v>
+        <v>22860.87919921875</v>
       </c>
       <c r="F45" t="n">
-        <v>2022.443597412109</v>
+        <v>2351.206024169921</v>
       </c>
     </row>
     <row r="46">
@@ -1539,10 +1539,10 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>17919.37999460697</v>
+        <v>18639.81430664062</v>
       </c>
       <c r="F46" t="n">
-        <v>2050.517663574219</v>
+        <v>1769.778125</v>
       </c>
     </row>
     <row r="47">
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>17701.56561582089</v>
+        <v>14661.73745117187</v>
       </c>
       <c r="F47" t="n">
-        <v>2309.829046630859</v>
+        <v>966.1082336425781</v>
       </c>
     </row>
     <row r="48">
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>14288.26326830387</v>
+        <v>6938.455932617187</v>
       </c>
       <c r="F48" t="n">
-        <v>1771.529095458984</v>
+        <v>638.1369232177734</v>
       </c>
     </row>
     <row r="49">
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>10651.05858440399</v>
+        <v>6739.509301757812</v>
       </c>
       <c r="F49" t="n">
-        <v>1095.897076416016</v>
+        <v>975.3493652343749</v>
       </c>
     </row>
     <row r="50">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>9453.193078517914</v>
+        <v>1975.967004394531</v>
       </c>
       <c r="F50" t="n">
-        <v>1305.603900146484</v>
+        <v>238.2653617858887</v>
       </c>
     </row>
     <row r="51">
@@ -1659,10 +1659,10 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>8644.841516208648</v>
+        <v>407.9443908691406</v>
       </c>
       <c r="F51" t="n">
-        <v>1028.387780761719</v>
+        <v>79.1364631652832</v>
       </c>
     </row>
     <row r="52">
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>23775.50928522109</v>
+        <v>33109.08712890624</v>
       </c>
       <c r="F52" t="n">
-        <v>2595.326015319824</v>
+        <v>2355.606585083007</v>
       </c>
     </row>
     <row r="53">
@@ -1707,10 +1707,10 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>22385.61007283688</v>
+        <v>30725.85947265624</v>
       </c>
       <c r="F53" t="n">
-        <v>2927.635943603515</v>
+        <v>2409.031742858887</v>
       </c>
     </row>
     <row r="54">
@@ -1731,10 +1731,10 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>21805.69786982238</v>
+        <v>29897.91764648437</v>
       </c>
       <c r="F54" t="n">
-        <v>2580.640485839843</v>
+        <v>2706.853996582031</v>
       </c>
     </row>
     <row r="55">
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>21402.44389051913</v>
+        <v>26290.01107910156</v>
       </c>
       <c r="F55" t="n">
-        <v>2325.810137023925</v>
+        <v>2703.886927795409</v>
       </c>
     </row>
     <row r="56">
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>20607.28699379801</v>
+        <v>21435.78645263672</v>
       </c>
       <c r="F56" t="n">
-        <v>2358.095313110351</v>
+        <v>2035.24484375</v>
       </c>
     </row>
     <row r="57">
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>20356.80045819402</v>
+        <v>16860.99806884765</v>
       </c>
       <c r="F57" t="n">
-        <v>2656.303403625487</v>
+        <v>1111.024468688965</v>
       </c>
     </row>
     <row r="58">
@@ -1827,10 +1827,10 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>16431.50275854944</v>
+        <v>7979.224322509765</v>
       </c>
       <c r="F58" t="n">
-        <v>2037.258459777831</v>
+        <v>733.8574617004393</v>
       </c>
     </row>
     <row r="59">
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>12248.71737206459</v>
+        <v>7750.435697021483</v>
       </c>
       <c r="F59" t="n">
-        <v>1260.281637878418</v>
+        <v>1121.651770019531</v>
       </c>
     </row>
     <row r="60">
@@ -1875,10 +1875,10 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>10871.1720402956</v>
+        <v>2272.362055053711</v>
       </c>
       <c r="F60" t="n">
-        <v>1501.444485168456</v>
+        <v>274.005166053772</v>
       </c>
     </row>
     <row r="61">
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>9941.567743639944</v>
+        <v>469.1360494995117</v>
       </c>
       <c r="F61" t="n">
-        <v>1182.645947875976</v>
+        <v>91.00693264007568</v>
       </c>
     </row>
     <row r="62">
@@ -1923,10 +1923,10 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>17977.70078277588</v>
+        <v>25035.2265625</v>
       </c>
       <c r="F62" t="n">
-        <v>1962.439331054688</v>
+        <v>1781.177001953125</v>
       </c>
     </row>
     <row r="63">
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>16926.73729515076</v>
+        <v>23233.1640625</v>
       </c>
       <c r="F63" t="n">
-        <v>2213.71337890625</v>
+        <v>1821.574096679688</v>
       </c>
     </row>
     <row r="64">
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>16488.24035525322</v>
+        <v>22607.12109375</v>
       </c>
       <c r="F64" t="n">
-        <v>1951.3349609375</v>
+        <v>2046.7705078125</v>
       </c>
     </row>
     <row r="65">
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>16183.32241249084</v>
+        <v>19879.025390625</v>
       </c>
       <c r="F65" t="n">
-        <v>1758.646606445312</v>
+        <v>2044.526977539062</v>
       </c>
     </row>
     <row r="66">
@@ -2019,10 +2019,10 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>15582.0695605278</v>
+        <v>16208.5341796875</v>
       </c>
       <c r="F66" t="n">
-        <v>1783.058837890625</v>
+        <v>1538.9375</v>
       </c>
     </row>
     <row r="67">
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>15392.66575288773</v>
+        <v>12749.3369140625</v>
       </c>
       <c r="F67" t="n">
-        <v>2008.546997070312</v>
+        <v>840.0941162109375</v>
       </c>
     </row>
     <row r="68">
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>12424.57675504684</v>
+        <v>6033.43994140625</v>
       </c>
       <c r="F68" t="n">
-        <v>1540.460083007812</v>
+        <v>554.9016723632812</v>
       </c>
     </row>
     <row r="69">
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>9261.790073394775</v>
+        <v>5860.44287109375</v>
       </c>
       <c r="F69" t="n">
-        <v>952.9539794921875</v>
+        <v>848.1298828125</v>
       </c>
     </row>
     <row r="70">
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>8220.167894363403</v>
+        <v>1718.232177734375</v>
       </c>
       <c r="F70" t="n">
-        <v>1135.307739257812</v>
+        <v>207.1872711181641</v>
       </c>
     </row>
     <row r="71">
@@ -2139,10 +2139,10 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>7517.253492355347</v>
+        <v>354.7342529296875</v>
       </c>
       <c r="F71" t="n">
-        <v>894.250244140625</v>
+        <v>68.81431579589844</v>
       </c>
     </row>
     <row r="72">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>21573.24093933106</v>
+        <v>30042.271875</v>
       </c>
       <c r="F72" t="n">
-        <v>2354.927197265626</v>
+        <v>2137.41240234375</v>
       </c>
     </row>
     <row r="73">
@@ -2187,10 +2187,10 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>20312.08475418091</v>
+        <v>27879.796875</v>
       </c>
       <c r="F73" t="n">
-        <v>2656.4560546875</v>
+        <v>2185.888916015625</v>
       </c>
     </row>
     <row r="74">
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>19785.88842630386</v>
+        <v>27128.5453125</v>
       </c>
       <c r="F74" t="n">
-        <v>2341.601953125</v>
+        <v>2456.124609375</v>
       </c>
     </row>
     <row r="75">
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>19419.98689498901</v>
+        <v>23854.83046875</v>
       </c>
       <c r="F75" t="n">
-        <v>2110.375927734374</v>
+        <v>2453.432373046875</v>
       </c>
     </row>
     <row r="76">
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>18698.48347263336</v>
+        <v>19450.241015625</v>
       </c>
       <c r="F76" t="n">
-        <v>2139.67060546875</v>
+        <v>1846.725</v>
       </c>
     </row>
     <row r="77">
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>18471.19890346528</v>
+        <v>15299.204296875</v>
       </c>
       <c r="F77" t="n">
-        <v>2410.256396484374</v>
+        <v>1008.112939453125</v>
       </c>
     </row>
     <row r="78">
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>14909.49210605621</v>
+        <v>7240.1279296875</v>
       </c>
       <c r="F78" t="n">
-        <v>1848.552099609374</v>
+        <v>665.8820068359374</v>
       </c>
     </row>
     <row r="79">
@@ -2331,10 +2331,10 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>11114.14808807373</v>
+        <v>7032.5314453125</v>
       </c>
       <c r="F79" t="n">
-        <v>1143.544775390625</v>
+        <v>1017.755859375</v>
       </c>
     </row>
     <row r="80">
@@ -2355,10 +2355,10 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>9864.201473236084</v>
+        <v>2061.87861328125</v>
       </c>
       <c r="F80" t="n">
-        <v>1362.369287109374</v>
+        <v>248.6247253417969</v>
       </c>
     </row>
     <row r="81">
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>9020.704190826416</v>
+        <v>425.681103515625</v>
       </c>
       <c r="F81" t="n">
-        <v>1073.10029296875</v>
+        <v>82.57717895507812</v>
       </c>
     </row>
     <row r="82">
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>25887.88912719726</v>
+        <v>36050.72625</v>
       </c>
       <c r="F82" t="n">
-        <v>2825.91263671875</v>
+        <v>2564.8948828125</v>
       </c>
     </row>
     <row r="83">
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>24374.50170501709</v>
+        <v>33455.75625</v>
       </c>
       <c r="F83" t="n">
-        <v>3187.747265625</v>
+        <v>2623.066699218751</v>
       </c>
     </row>
     <row r="84">
@@ -2451,10 +2451,10 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>23743.06611156464</v>
+        <v>32554.254375</v>
       </c>
       <c r="F84" t="n">
-        <v>2809.92234375</v>
+        <v>2947.34953125</v>
       </c>
     </row>
     <row r="85">
@@ -2475,10 +2475,10 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>23303.98427398681</v>
+        <v>28625.7965625</v>
       </c>
       <c r="F85" t="n">
-        <v>2532.451113281249</v>
+        <v>2944.118847656249</v>
       </c>
     </row>
     <row r="86">
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>22438.18016716003</v>
+        <v>23340.28921875</v>
       </c>
       <c r="F86" t="n">
-        <v>2567.6047265625</v>
+        <v>2216.07</v>
       </c>
     </row>
     <row r="87">
@@ -2523,10 +2523,10 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>22165.43868415833</v>
+        <v>18359.04515625</v>
       </c>
       <c r="F87" t="n">
-        <v>2892.307675781249</v>
+        <v>1209.73552734375</v>
       </c>
     </row>
     <row r="88">
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>17891.39052726745</v>
+        <v>8688.153515624999</v>
       </c>
       <c r="F88" t="n">
-        <v>2218.262519531249</v>
+        <v>799.0584082031249</v>
       </c>
     </row>
     <row r="89">
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>13336.97770568848</v>
+        <v>8439.037734375001</v>
       </c>
       <c r="F89" t="n">
-        <v>1372.25373046875</v>
+        <v>1221.30703125</v>
       </c>
     </row>
     <row r="90">
@@ -2595,10 +2595,10 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>11837.0417678833</v>
+        <v>2474.2543359375</v>
       </c>
       <c r="F90" t="n">
-        <v>1634.843144531249</v>
+        <v>298.3496704101563</v>
       </c>
     </row>
     <row r="91">
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>10824.8450289917</v>
+        <v>510.81732421875</v>
       </c>
       <c r="F91" t="n">
-        <v>1287.7203515625</v>
+        <v>99.09261474609374</v>
       </c>
     </row>
   </sheetData>
@@ -5377,10 +5377,10 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>11240</v>
+        <v>11160</v>
       </c>
       <c r="F83" t="n">
-        <v>12920</v>
+        <v>12828</v>
       </c>
       <c r="G83" t="n">
         <v>14.94</v>
@@ -5781,7 +5781,7 @@
         <v>0.9203</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9952</v>
+        <v>0.9956</v>
       </c>
       <c r="H2" t="n">
         <v>0.875</v>
@@ -5790,25 +5790,25 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9106</v>
+        <v>0.9121</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1079</v>
+        <v>0.1503</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1570</v>
+        <v>1424.9</v>
       </c>
       <c r="Q2" t="n">
         <v>13885</v>
@@ -5838,7 +5838,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9941</v>
+        <v>0.9951</v>
       </c>
       <c r="H3" t="n">
         <v>0.8125</v>
@@ -5847,25 +5847,25 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9497</v>
+        <v>0.9505</v>
       </c>
       <c r="N3" t="n">
-        <v>0.11</v>
+        <v>0.1509</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1771</v>
+        <v>1457.3</v>
       </c>
       <c r="Q3" t="n">
         <v>12828</v>
@@ -5895,7 +5895,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9943</v>
+        <v>0.9941</v>
       </c>
       <c r="H4" t="n">
         <v>0.0625</v>
@@ -5904,25 +5904,25 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7493</v>
+        <v>0.7536</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1272</v>
+        <v>0.1744</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1561.1</v>
+        <v>1637.4</v>
       </c>
       <c r="Q4" t="n">
         <v>10805</v>
@@ -5952,7 +5952,7 @@
         <v>0.9193</v>
       </c>
       <c r="G5" t="n">
-        <v>0.996</v>
+        <v>0.9954</v>
       </c>
       <c r="H5" t="n">
         <v>0.3125</v>
@@ -5961,25 +5961,25 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.7638</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1128</v>
+        <v>0.1386</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1406.9</v>
+        <v>1635.6</v>
       </c>
       <c r="Q5" t="n">
         <v>11954</v>
@@ -6009,7 +6009,7 @@
         <v>0.9098000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9937</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>0.5625</v>
@@ -6018,25 +6018,25 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8197</v>
+        <v>0.8228</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1565</v>
+        <v>0.1628</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1426.4</v>
+        <v>1231.2</v>
       </c>
       <c r="Q6" t="n">
         <v>8299</v>
@@ -6066,7 +6066,7 @@
         <v>0.9466</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9948</v>
+        <v>0.9978</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -6075,25 +6075,25 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6952</v>
+        <v>0.7007</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1234</v>
+        <v>0.1022</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1606.8</v>
+        <v>672.1</v>
       </c>
       <c r="Q7" t="n">
         <v>10391</v>
@@ -6123,7 +6123,7 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9933999999999999</v>
+        <v>0.9976</v>
       </c>
       <c r="H8" t="n">
         <v>0.625</v>
@@ -6132,25 +6132,25 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8996</v>
+        <v>0.9014</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2085</v>
+        <v>0.1013</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1232.4</v>
+        <v>443.9</v>
       </c>
       <c r="Q8" t="n">
         <v>4966</v>
@@ -6180,7 +6180,7 @@
         <v>0.9353</v>
       </c>
       <c r="G9" t="n">
-        <v>0.997</v>
+        <v>0.9973</v>
       </c>
       <c r="H9" t="n">
         <v>0.6875</v>
@@ -6189,25 +6189,25 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8711</v>
+        <v>0.8733</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1199</v>
+        <v>0.0759</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>762.4</v>
+        <v>678.5</v>
       </c>
       <c r="Q9" t="n">
         <v>6437</v>
@@ -6237,7 +6237,7 @@
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>0.994</v>
+        <v>0.9989</v>
       </c>
       <c r="H10" t="n">
         <v>0.1562</v>
@@ -6246,25 +6246,25 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7743</v>
+        <v>0.7785</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1552</v>
+        <v>0.0324</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>908.2</v>
+        <v>165.7</v>
       </c>
       <c r="Q10" t="n">
         <v>4414</v>
@@ -6294,7 +6294,7 @@
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9965000000000001</v>
+        <v>0.9997</v>
       </c>
       <c r="H11" t="n">
         <v>0.09370000000000001</v>
@@ -6303,25 +6303,25 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7577</v>
+        <v>0.7621</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1056</v>
+        <v>0.005</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>715.4</v>
+        <v>55.1</v>
       </c>
       <c r="Q11" t="n">
         <v>5931</v>
@@ -6351,7 +6351,7 @@
         <v>0.9203</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9947</v>
+        <v>0.9952</v>
       </c>
       <c r="H12" t="n">
         <v>0.875</v>
@@ -6360,25 +6360,25 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9106</v>
+        <v>0.9121</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1187</v>
+        <v>0.1653</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1726.9</v>
+        <v>1567.4</v>
       </c>
       <c r="Q12" t="n">
         <v>13885</v>
@@ -6408,7 +6408,7 @@
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9935</v>
+        <v>0.9946</v>
       </c>
       <c r="H13" t="n">
         <v>0.8125</v>
@@ -6417,25 +6417,25 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9497</v>
+        <v>0.9505</v>
       </c>
       <c r="N13" t="n">
-        <v>0.121</v>
+        <v>0.166</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1948.1</v>
+        <v>1603</v>
       </c>
       <c r="Q13" t="n">
         <v>12828</v>
@@ -6465,7 +6465,7 @@
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9938</v>
+        <v>0.9935</v>
       </c>
       <c r="H14" t="n">
         <v>0.0625</v>
@@ -6474,25 +6474,25 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7492</v>
+        <v>0.7536</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1399</v>
+        <v>0.1918</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1717.2</v>
+        <v>1801.2</v>
       </c>
       <c r="Q14" t="n">
         <v>10805</v>
@@ -6522,7 +6522,7 @@
         <v>0.9193</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9956</v>
+        <v>0.9949</v>
       </c>
       <c r="H15" t="n">
         <v>0.3125</v>
@@ -6531,25 +6531,25 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.7638</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1241</v>
+        <v>0.1524</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1547.6</v>
+        <v>1799.2</v>
       </c>
       <c r="Q15" t="n">
         <v>11954</v>
@@ -6579,7 +6579,7 @@
         <v>0.9098000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.993</v>
+        <v>0.994</v>
       </c>
       <c r="H16" t="n">
         <v>0.5625</v>
@@ -6588,25 +6588,25 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8197</v>
+        <v>0.8228</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1721</v>
+        <v>0.179</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1569.1</v>
+        <v>1354.3</v>
       </c>
       <c r="Q16" t="n">
         <v>8299</v>
@@ -6636,7 +6636,7 @@
         <v>0.9466</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9943</v>
+        <v>0.9976</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -6645,25 +6645,25 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6951000000000001</v>
+        <v>0.7006</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1358</v>
+        <v>0.1125</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1767.5</v>
+        <v>739.3</v>
       </c>
       <c r="Q17" t="n">
         <v>10391</v>
@@ -6693,7 +6693,7 @@
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9927</v>
+        <v>0.9974</v>
       </c>
       <c r="H18" t="n">
         <v>0.625</v>
@@ -6702,25 +6702,25 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8995</v>
+        <v>0.9014</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2294</v>
+        <v>0.1114</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1355.6</v>
+        <v>488.3</v>
       </c>
       <c r="Q18" t="n">
         <v>4966</v>
@@ -6750,7 +6750,7 @@
         <v>0.9353</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9967</v>
+        <v>0.9971</v>
       </c>
       <c r="H19" t="n">
         <v>0.6875</v>
@@ -6759,25 +6759,25 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8711</v>
+        <v>0.8733</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1319</v>
+        <v>0.0835</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>838.6</v>
+        <v>746.4</v>
       </c>
       <c r="Q19" t="n">
         <v>6437</v>
@@ -6807,7 +6807,7 @@
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9933999999999999</v>
+        <v>0.9988</v>
       </c>
       <c r="H20" t="n">
         <v>0.1562</v>
@@ -6816,25 +6816,25 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7743</v>
+        <v>0.7785</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1707</v>
+        <v>0.0357</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>999.1</v>
+        <v>182.3</v>
       </c>
       <c r="Q20" t="n">
         <v>4414</v>
@@ -6864,7 +6864,7 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9962</v>
+        <v>0.9997</v>
       </c>
       <c r="H21" t="n">
         <v>0.09370000000000001</v>
@@ -6873,25 +6873,25 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7577</v>
+        <v>0.7621</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1162</v>
+        <v>0.0055</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>786.9</v>
+        <v>60.6</v>
       </c>
       <c r="Q21" t="n">
         <v>5931</v>
@@ -6921,7 +6921,7 @@
         <v>0.9203</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9942</v>
+        <v>0.9947</v>
       </c>
       <c r="H22" t="n">
         <v>0.875</v>
@@ -6930,25 +6930,25 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4137</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4284</v>
+        <v>0.0495</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1578</v>
+        <v>0.2625</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9448</v>
+        <v>0.9121</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1306</v>
+        <v>0.1818</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1899.6</v>
+        <v>1724.2</v>
       </c>
       <c r="Q22" t="n">
         <v>13885</v>
@@ -6978,7 +6978,7 @@
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9796</v>
+        <v>0.9941</v>
       </c>
       <c r="H23" t="n">
         <v>0.8125</v>
@@ -6987,25 +6987,25 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4137</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4284</v>
+        <v>0.0495</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1578</v>
+        <v>0.2625</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9617</v>
+        <v>0.9505</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1331</v>
+        <v>0.1826</v>
       </c>
       <c r="O23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2142.9</v>
+        <v>1763.3</v>
       </c>
       <c r="Q23" t="n">
         <v>12828</v>
@@ -7035,7 +7035,7 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9932</v>
+        <v>0.9928</v>
       </c>
       <c r="H24" t="n">
         <v>0.0625</v>
@@ -7044,25 +7044,25 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4137</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>0.4284</v>
+        <v>0.0495</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1578</v>
+        <v>0.2625</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8491</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1539</v>
+        <v>0.211</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1888.9</v>
+        <v>1981.3</v>
       </c>
       <c r="Q24" t="n">
         <v>10805</v>
@@ -7092,7 +7092,7 @@
         <v>0.9193</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9952</v>
+        <v>0.9944</v>
       </c>
       <c r="H25" t="n">
         <v>0.3125</v>
@@ -7101,25 +7101,25 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.4137</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>0.4284</v>
+        <v>0.0495</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1578</v>
+        <v>0.2625</v>
       </c>
       <c r="M25" t="n">
-        <v>0.856</v>
+        <v>0.7637</v>
       </c>
       <c r="N25" t="n">
-        <v>0.1365</v>
+        <v>0.1677</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1702.4</v>
+        <v>1979.1</v>
       </c>
       <c r="Q25" t="n">
         <v>11954</v>
@@ -7149,7 +7149,7 @@
         <v>0.9098000000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9923</v>
+        <v>0.9933999999999999</v>
       </c>
       <c r="H26" t="n">
         <v>0.5625</v>
@@ -7158,25 +7158,25 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0.4137</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.4284</v>
+        <v>0.0495</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1578</v>
+        <v>0.2625</v>
       </c>
       <c r="M26" t="n">
-        <v>0.8903</v>
+        <v>0.8228</v>
       </c>
       <c r="N26" t="n">
-        <v>0.1893</v>
+        <v>0.1969</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1726</v>
+        <v>1489.7</v>
       </c>
       <c r="Q26" t="n">
         <v>8299</v>
@@ -7206,7 +7206,7 @@
         <v>0.9466</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9937</v>
+        <v>0.9974</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -7215,25 +7215,25 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.4137</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>0.4284</v>
+        <v>0.0495</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1578</v>
+        <v>0.2625</v>
       </c>
       <c r="M27" t="n">
-        <v>0.8174</v>
+        <v>0.7006</v>
       </c>
       <c r="N27" t="n">
-        <v>0.1494</v>
+        <v>0.1237</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1944.3</v>
+        <v>813.2</v>
       </c>
       <c r="Q27" t="n">
         <v>10391</v>
@@ -7263,7 +7263,7 @@
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>0.992</v>
+        <v>0.9971</v>
       </c>
       <c r="H28" t="n">
         <v>0.625</v>
@@ -7272,25 +7272,25 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0.4137</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.4284</v>
+        <v>0.0495</v>
       </c>
       <c r="L28" t="n">
-        <v>0.1578</v>
+        <v>0.2625</v>
       </c>
       <c r="M28" t="n">
-        <v>0.9374</v>
+        <v>0.9014</v>
       </c>
       <c r="N28" t="n">
-        <v>0.2523</v>
+        <v>0.1225</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1491.2</v>
+        <v>537.1</v>
       </c>
       <c r="Q28" t="n">
         <v>4966</v>
@@ -7320,7 +7320,7 @@
         <v>0.9353</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9964</v>
+        <v>0.9968</v>
       </c>
       <c r="H29" t="n">
         <v>0.6875</v>
@@ -7329,25 +7329,25 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0.4137</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>0.4284</v>
+        <v>0.0495</v>
       </c>
       <c r="L29" t="n">
-        <v>0.1578</v>
+        <v>0.2625</v>
       </c>
       <c r="M29" t="n">
-        <v>0.9224</v>
+        <v>0.8733</v>
       </c>
       <c r="N29" t="n">
-        <v>0.1451</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>922.5</v>
+        <v>821</v>
       </c>
       <c r="Q29" t="n">
         <v>6437</v>
@@ -7377,7 +7377,7 @@
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>0.9928</v>
+        <v>0.9987</v>
       </c>
       <c r="H30" t="n">
         <v>0.1562</v>
@@ -7386,25 +7386,25 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.4137</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>0.4284</v>
+        <v>0.0495</v>
       </c>
       <c r="L30" t="n">
-        <v>0.1578</v>
+        <v>0.2625</v>
       </c>
       <c r="M30" t="n">
-        <v>0.8637</v>
+        <v>0.7784</v>
       </c>
       <c r="N30" t="n">
-        <v>0.1878</v>
+        <v>0.0393</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1099</v>
+        <v>200.6</v>
       </c>
       <c r="Q30" t="n">
         <v>4414</v>
@@ -7434,7 +7434,7 @@
         <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9958</v>
+        <v>0.9997</v>
       </c>
       <c r="H31" t="n">
         <v>0.09370000000000001</v>
@@ -7443,25 +7443,25 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0.4137</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>0.4284</v>
+        <v>0.0495</v>
       </c>
       <c r="L31" t="n">
-        <v>0.1578</v>
+        <v>0.2625</v>
       </c>
       <c r="M31" t="n">
-        <v>0.8551</v>
+        <v>0.7621</v>
       </c>
       <c r="N31" t="n">
-        <v>0.1278</v>
+        <v>0.006</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>865.6</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="Q31" t="n">
         <v>5931</v>
@@ -7491,7 +7491,7 @@
         <v>0.9203</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9952</v>
+        <v>0.9956</v>
       </c>
       <c r="H32" t="n">
         <v>0.875</v>
@@ -7500,25 +7500,25 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L32" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M32" t="n">
-        <v>0.9106</v>
+        <v>0.9121</v>
       </c>
       <c r="N32" t="n">
-        <v>0.1079</v>
+        <v>0.1503</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1570</v>
+        <v>1424.9</v>
       </c>
       <c r="Q32" t="n">
         <v>13885</v>
@@ -7548,7 +7548,7 @@
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9941</v>
+        <v>0.9951</v>
       </c>
       <c r="H33" t="n">
         <v>0.8125</v>
@@ -7557,25 +7557,25 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M33" t="n">
-        <v>0.9497</v>
+        <v>0.9505</v>
       </c>
       <c r="N33" t="n">
-        <v>0.11</v>
+        <v>0.1509</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1771</v>
+        <v>1457.3</v>
       </c>
       <c r="Q33" t="n">
         <v>12828</v>
@@ -7605,7 +7605,7 @@
         <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9943</v>
+        <v>0.9941</v>
       </c>
       <c r="H34" t="n">
         <v>0.0625</v>
@@ -7614,25 +7614,25 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L34" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M34" t="n">
-        <v>0.7493</v>
+        <v>0.7536</v>
       </c>
       <c r="N34" t="n">
-        <v>0.1272</v>
+        <v>0.1744</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1561.1</v>
+        <v>1637.4</v>
       </c>
       <c r="Q34" t="n">
         <v>10805</v>
@@ -7662,7 +7662,7 @@
         <v>0.9193</v>
       </c>
       <c r="G35" t="n">
-        <v>0.996</v>
+        <v>0.9954</v>
       </c>
       <c r="H35" t="n">
         <v>0.3125</v>
@@ -7671,25 +7671,25 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M35" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.7638</v>
       </c>
       <c r="N35" t="n">
-        <v>0.1128</v>
+        <v>0.1386</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1406.9</v>
+        <v>1635.6</v>
       </c>
       <c r="Q35" t="n">
         <v>11954</v>
@@ -7719,7 +7719,7 @@
         <v>0.9098000000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>0.9937</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="H36" t="n">
         <v>0.5625</v>
@@ -7728,25 +7728,25 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L36" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M36" t="n">
-        <v>0.8197</v>
+        <v>0.8228</v>
       </c>
       <c r="N36" t="n">
-        <v>0.1565</v>
+        <v>0.1628</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1426.4</v>
+        <v>1231.2</v>
       </c>
       <c r="Q36" t="n">
         <v>8299</v>
@@ -7776,7 +7776,7 @@
         <v>0.9466</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9948</v>
+        <v>0.9978</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -7785,25 +7785,25 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L37" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M37" t="n">
-        <v>0.6952</v>
+        <v>0.7007</v>
       </c>
       <c r="N37" t="n">
-        <v>0.1234</v>
+        <v>0.1022</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1606.8</v>
+        <v>672.1</v>
       </c>
       <c r="Q37" t="n">
         <v>10391</v>
@@ -7833,7 +7833,7 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0.9933999999999999</v>
+        <v>0.9976</v>
       </c>
       <c r="H38" t="n">
         <v>0.625</v>
@@ -7842,25 +7842,25 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L38" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M38" t="n">
-        <v>0.8996</v>
+        <v>0.9014</v>
       </c>
       <c r="N38" t="n">
-        <v>0.2085</v>
+        <v>0.1013</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1232.4</v>
+        <v>443.9</v>
       </c>
       <c r="Q38" t="n">
         <v>4966</v>
@@ -7890,7 +7890,7 @@
         <v>0.9353</v>
       </c>
       <c r="G39" t="n">
-        <v>0.997</v>
+        <v>0.9973</v>
       </c>
       <c r="H39" t="n">
         <v>0.6875</v>
@@ -7899,25 +7899,25 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L39" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M39" t="n">
-        <v>0.8711</v>
+        <v>0.8733</v>
       </c>
       <c r="N39" t="n">
-        <v>0.1199</v>
+        <v>0.0759</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>762.4</v>
+        <v>678.5</v>
       </c>
       <c r="Q39" t="n">
         <v>6437</v>
@@ -7947,7 +7947,7 @@
         <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>0.994</v>
+        <v>0.9989</v>
       </c>
       <c r="H40" t="n">
         <v>0.1562</v>
@@ -7956,25 +7956,25 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L40" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M40" t="n">
-        <v>0.7743</v>
+        <v>0.7785</v>
       </c>
       <c r="N40" t="n">
-        <v>0.1552</v>
+        <v>0.0324</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>908.2</v>
+        <v>165.7</v>
       </c>
       <c r="Q40" t="n">
         <v>4414</v>
@@ -8004,7 +8004,7 @@
         <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>0.9965000000000001</v>
+        <v>0.9997</v>
       </c>
       <c r="H41" t="n">
         <v>0.09370000000000001</v>
@@ -8013,25 +8013,25 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M41" t="n">
-        <v>0.7577</v>
+        <v>0.7621</v>
       </c>
       <c r="N41" t="n">
-        <v>0.1056</v>
+        <v>0.005</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>715.4</v>
+        <v>55.1</v>
       </c>
       <c r="Q41" t="n">
         <v>5931</v>
@@ -8061,7 +8061,7 @@
         <v>0.9203</v>
       </c>
       <c r="G42" t="n">
-        <v>0.9944</v>
+        <v>0.995</v>
       </c>
       <c r="H42" t="n">
         <v>0.875</v>
@@ -8070,25 +8070,25 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L42" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M42" t="n">
-        <v>0.9106</v>
+        <v>0.9121</v>
       </c>
       <c r="N42" t="n">
-        <v>0.1241</v>
+        <v>0.1728</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>1805.4</v>
+        <v>1638.7</v>
       </c>
       <c r="Q42" t="n">
         <v>13885</v>
@@ -8118,7 +8118,7 @@
         <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>0.9932</v>
+        <v>0.9944</v>
       </c>
       <c r="H43" t="n">
         <v>0.8125</v>
@@ -8127,25 +8127,25 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L43" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M43" t="n">
-        <v>0.9497</v>
+        <v>0.9505</v>
       </c>
       <c r="N43" t="n">
-        <v>0.1265</v>
+        <v>0.1736</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2036.6</v>
+        <v>1675.8</v>
       </c>
       <c r="Q43" t="n">
         <v>12828</v>
@@ -8175,7 +8175,7 @@
         <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>0.9935</v>
+        <v>0.9932</v>
       </c>
       <c r="H44" t="n">
         <v>0.0625</v>
@@ -8184,25 +8184,25 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L44" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M44" t="n">
-        <v>0.7492</v>
+        <v>0.7536</v>
       </c>
       <c r="N44" t="n">
-        <v>0.1462</v>
+        <v>0.2005</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>1795.2</v>
+        <v>1883</v>
       </c>
       <c r="Q44" t="n">
         <v>10805</v>
@@ -8232,7 +8232,7 @@
         <v>0.9193</v>
       </c>
       <c r="G45" t="n">
-        <v>0.9954</v>
+        <v>0.9947</v>
       </c>
       <c r="H45" t="n">
         <v>0.3125</v>
@@ -8241,25 +8241,25 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L45" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M45" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.7637</v>
       </c>
       <c r="N45" t="n">
-        <v>0.1297</v>
+        <v>0.1594</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>1618</v>
+        <v>1881</v>
       </c>
       <c r="Q45" t="n">
         <v>11954</v>
@@ -8289,7 +8289,7 @@
         <v>0.9098000000000001</v>
       </c>
       <c r="G46" t="n">
-        <v>0.9927</v>
+        <v>0.9937</v>
       </c>
       <c r="H46" t="n">
         <v>0.5625</v>
@@ -8298,25 +8298,25 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L46" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M46" t="n">
-        <v>0.8197</v>
+        <v>0.8228</v>
       </c>
       <c r="N46" t="n">
-        <v>0.1799</v>
+        <v>0.1872</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>1640.4</v>
+        <v>1415.8</v>
       </c>
       <c r="Q46" t="n">
         <v>8299</v>
@@ -8346,7 +8346,7 @@
         <v>0.9466</v>
       </c>
       <c r="G47" t="n">
-        <v>0.994</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -8355,25 +8355,25 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L47" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M47" t="n">
-        <v>0.6951000000000001</v>
+        <v>0.7006</v>
       </c>
       <c r="N47" t="n">
-        <v>0.142</v>
+        <v>0.1176</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>1847.9</v>
+        <v>772.9</v>
       </c>
       <c r="Q47" t="n">
         <v>10391</v>
@@ -8403,7 +8403,7 @@
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.9973</v>
       </c>
       <c r="H48" t="n">
         <v>0.625</v>
@@ -8412,25 +8412,25 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L48" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M48" t="n">
-        <v>0.8995</v>
+        <v>0.9014</v>
       </c>
       <c r="N48" t="n">
-        <v>0.2398</v>
+        <v>0.1164</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>1417.2</v>
+        <v>510.5</v>
       </c>
       <c r="Q48" t="n">
         <v>4966</v>
@@ -8460,7 +8460,7 @@
         <v>0.9353</v>
       </c>
       <c r="G49" t="n">
-        <v>0.9966</v>
+        <v>0.9969</v>
       </c>
       <c r="H49" t="n">
         <v>0.6875</v>
@@ -8469,25 +8469,25 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L49" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M49" t="n">
-        <v>0.871</v>
+        <v>0.8733</v>
       </c>
       <c r="N49" t="n">
-        <v>0.1379</v>
+        <v>0.0873</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>876.7</v>
+        <v>780.3</v>
       </c>
       <c r="Q49" t="n">
         <v>6437</v>
@@ -8517,7 +8517,7 @@
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>0.9931</v>
+        <v>0.9987</v>
       </c>
       <c r="H50" t="n">
         <v>0.1562</v>
@@ -8526,25 +8526,25 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L50" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M50" t="n">
-        <v>0.7743</v>
+        <v>0.7785</v>
       </c>
       <c r="N50" t="n">
-        <v>0.1785</v>
+        <v>0.0373</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>1044.5</v>
+        <v>190.6</v>
       </c>
       <c r="Q50" t="n">
         <v>4414</v>
@@ -8574,7 +8574,7 @@
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>0.996</v>
+        <v>0.9997</v>
       </c>
       <c r="H51" t="n">
         <v>0.09370000000000001</v>
@@ -8583,25 +8583,25 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L51" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M51" t="n">
-        <v>0.7577</v>
+        <v>0.7621</v>
       </c>
       <c r="N51" t="n">
-        <v>0.1215</v>
+        <v>0.0057</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>822.7</v>
+        <v>63.3</v>
       </c>
       <c r="Q51" t="n">
         <v>5931</v>
@@ -8631,7 +8631,7 @@
         <v>0.9203</v>
       </c>
       <c r="G52" t="n">
-        <v>0.9936</v>
+        <v>0.9942</v>
       </c>
       <c r="H52" t="n">
         <v>0.875</v>
@@ -8640,25 +8640,25 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>0.3072</v>
+        <v>0.3819</v>
       </c>
       <c r="K52" t="n">
-        <v>0.5756</v>
+        <v>0.4724</v>
       </c>
       <c r="L52" t="n">
-        <v>0.1172</v>
+        <v>0.1457</v>
       </c>
       <c r="M52" t="n">
-        <v>0.9572000000000001</v>
+        <v>0.9486</v>
       </c>
       <c r="N52" t="n">
-        <v>0.1427</v>
+        <v>0.1987</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>2076.3</v>
+        <v>1884.5</v>
       </c>
       <c r="Q52" t="n">
         <v>13885</v>
@@ -8688,7 +8688,7 @@
         <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>0.8847</v>
+        <v>0.9935</v>
       </c>
       <c r="H53" t="n">
         <v>0.8125</v>
@@ -8697,25 +8697,25 @@
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0.3072</v>
+        <v>0.3819</v>
       </c>
       <c r="K53" t="n">
-        <v>0.5756</v>
+        <v>0.4724</v>
       </c>
       <c r="L53" t="n">
-        <v>0.1172</v>
+        <v>0.1457</v>
       </c>
       <c r="M53" t="n">
-        <v>0.9117</v>
+        <v>0.9696</v>
       </c>
       <c r="N53" t="n">
-        <v>0.1454</v>
+        <v>0.1996</v>
       </c>
       <c r="O53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>2342.1</v>
+        <v>1927.2</v>
       </c>
       <c r="Q53" t="n">
         <v>12828</v>
@@ -8745,7 +8745,7 @@
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>0.9925</v>
+        <v>0.9688</v>
       </c>
       <c r="H54" t="n">
         <v>0.0625</v>
@@ -8754,25 +8754,25 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0.3072</v>
+        <v>0.3819</v>
       </c>
       <c r="K54" t="n">
-        <v>0.5756</v>
+        <v>0.4724</v>
       </c>
       <c r="L54" t="n">
-        <v>0.1172</v>
+        <v>0.1457</v>
       </c>
       <c r="M54" t="n">
-        <v>0.8858</v>
+        <v>0.8487</v>
       </c>
       <c r="N54" t="n">
-        <v>0.1682</v>
+        <v>0.2306</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P54" t="n">
-        <v>2064.5</v>
+        <v>2165.5</v>
       </c>
       <c r="Q54" t="n">
         <v>10805</v>
@@ -8802,7 +8802,7 @@
         <v>0.9193</v>
       </c>
       <c r="G55" t="n">
-        <v>0.9947</v>
+        <v>0.9699</v>
       </c>
       <c r="H55" t="n">
         <v>0.3125</v>
@@ -8811,25 +8811,25 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>0.3072</v>
+        <v>0.3819</v>
       </c>
       <c r="K55" t="n">
-        <v>0.5756</v>
+        <v>0.4724</v>
       </c>
       <c r="L55" t="n">
-        <v>0.1172</v>
+        <v>0.1457</v>
       </c>
       <c r="M55" t="n">
-        <v>0.8915999999999999</v>
+        <v>0.8548</v>
       </c>
       <c r="N55" t="n">
-        <v>0.1492</v>
+        <v>0.1833</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P55" t="n">
-        <v>1860.6</v>
+        <v>2163.1</v>
       </c>
       <c r="Q55" t="n">
         <v>11954</v>
@@ -8859,7 +8859,7 @@
         <v>0.9098000000000001</v>
       </c>
       <c r="G56" t="n">
-        <v>0.9916</v>
+        <v>0.9928</v>
       </c>
       <c r="H56" t="n">
         <v>0.5625</v>
@@ -8868,25 +8868,25 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0.3072</v>
+        <v>0.3819</v>
       </c>
       <c r="K56" t="n">
-        <v>0.5756</v>
+        <v>0.4724</v>
       </c>
       <c r="L56" t="n">
-        <v>0.1172</v>
+        <v>0.1457</v>
       </c>
       <c r="M56" t="n">
-        <v>0.9162</v>
+        <v>0.8984</v>
       </c>
       <c r="N56" t="n">
-        <v>0.2069</v>
+        <v>0.2152</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>1886.5</v>
+        <v>1628.2</v>
       </c>
       <c r="Q56" t="n">
         <v>8299</v>
@@ -8916,7 +8916,7 @@
         <v>0.9466</v>
       </c>
       <c r="G57" t="n">
-        <v>0.9881</v>
+        <v>0.9971</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -8925,25 +8925,25 @@
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>0.3072</v>
+        <v>0.3819</v>
       </c>
       <c r="K57" t="n">
-        <v>0.5756</v>
+        <v>0.4724</v>
       </c>
       <c r="L57" t="n">
-        <v>0.1172</v>
+        <v>0.1457</v>
       </c>
       <c r="M57" t="n">
-        <v>0.8595</v>
+        <v>0.8325</v>
       </c>
       <c r="N57" t="n">
-        <v>0.1633</v>
+        <v>0.1352</v>
       </c>
       <c r="O57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>2125</v>
+        <v>888.8</v>
       </c>
       <c r="Q57" t="n">
         <v>10391</v>
@@ -8973,7 +8973,7 @@
         <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>0.9912</v>
+        <v>0.9968</v>
       </c>
       <c r="H58" t="n">
         <v>0.625</v>
@@ -8982,25 +8982,25 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0.3072</v>
+        <v>0.3819</v>
       </c>
       <c r="K58" t="n">
-        <v>0.5756</v>
+        <v>0.4724</v>
       </c>
       <c r="L58" t="n">
-        <v>0.1172</v>
+        <v>0.1457</v>
       </c>
       <c r="M58" t="n">
-        <v>0.951</v>
+        <v>0.9439</v>
       </c>
       <c r="N58" t="n">
-        <v>0.2758</v>
+        <v>0.1339</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>1629.8</v>
+        <v>587.1</v>
       </c>
       <c r="Q58" t="n">
         <v>4966</v>
@@ -9030,7 +9030,7 @@
         <v>0.9353</v>
       </c>
       <c r="G59" t="n">
-        <v>0.996</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="H59" t="n">
         <v>0.6875</v>
@@ -9039,25 +9039,25 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>0.3072</v>
+        <v>0.3819</v>
       </c>
       <c r="K59" t="n">
-        <v>0.5756</v>
+        <v>0.4724</v>
       </c>
       <c r="L59" t="n">
-        <v>0.1172</v>
+        <v>0.1457</v>
       </c>
       <c r="M59" t="n">
-        <v>0.9412</v>
+        <v>0.9281</v>
       </c>
       <c r="N59" t="n">
-        <v>0.1586</v>
+        <v>0.1003</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>1008.2</v>
+        <v>897.3</v>
       </c>
       <c r="Q59" t="n">
         <v>6437</v>
@@ -9087,7 +9087,7 @@
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>0.9921</v>
+        <v>0.9986</v>
       </c>
       <c r="H60" t="n">
         <v>0.1562</v>
@@ -9096,25 +9096,25 @@
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>0.3072</v>
+        <v>0.3819</v>
       </c>
       <c r="K60" t="n">
-        <v>0.5756</v>
+        <v>0.4724</v>
       </c>
       <c r="L60" t="n">
-        <v>0.1172</v>
+        <v>0.1457</v>
       </c>
       <c r="M60" t="n">
-        <v>0.8966</v>
+        <v>0.8764</v>
       </c>
       <c r="N60" t="n">
-        <v>0.2052</v>
+        <v>0.0429</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>1201.2</v>
+        <v>219.2</v>
       </c>
       <c r="Q60" t="n">
         <v>4414</v>
@@ -9144,7 +9144,7 @@
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>0.9954</v>
+        <v>0.9996</v>
       </c>
       <c r="H61" t="n">
         <v>0.09370000000000001</v>
@@ -9153,25 +9153,25 @@
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>0.3072</v>
+        <v>0.3819</v>
       </c>
       <c r="K61" t="n">
-        <v>0.5756</v>
+        <v>0.4724</v>
       </c>
       <c r="L61" t="n">
-        <v>0.1172</v>
+        <v>0.1457</v>
       </c>
       <c r="M61" t="n">
-        <v>0.8911</v>
+        <v>0.8678</v>
       </c>
       <c r="N61" t="n">
-        <v>0.1397</v>
+        <v>0.0066</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>946.1</v>
+        <v>72.8</v>
       </c>
       <c r="Q61" t="n">
         <v>5931</v>
@@ -9201,7 +9201,7 @@
         <v>0.9203</v>
       </c>
       <c r="G62" t="n">
-        <v>0.9952</v>
+        <v>0.9956</v>
       </c>
       <c r="H62" t="n">
         <v>0.875</v>
@@ -9210,25 +9210,25 @@
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K62" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L62" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M62" t="n">
-        <v>0.9106</v>
+        <v>0.9121</v>
       </c>
       <c r="N62" t="n">
-        <v>0.1079</v>
+        <v>0.1503</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>1570</v>
+        <v>1424.9</v>
       </c>
       <c r="Q62" t="n">
         <v>13885</v>
@@ -9258,7 +9258,7 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0.9941</v>
+        <v>0.9951</v>
       </c>
       <c r="H63" t="n">
         <v>0.8125</v>
@@ -9267,25 +9267,25 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L63" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M63" t="n">
-        <v>0.9497</v>
+        <v>0.9505</v>
       </c>
       <c r="N63" t="n">
-        <v>0.11</v>
+        <v>0.1509</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>1771</v>
+        <v>1457.3</v>
       </c>
       <c r="Q63" t="n">
         <v>12828</v>
@@ -9315,7 +9315,7 @@
         <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>0.9943</v>
+        <v>0.9941</v>
       </c>
       <c r="H64" t="n">
         <v>0.0625</v>
@@ -9324,25 +9324,25 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L64" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M64" t="n">
-        <v>0.7493</v>
+        <v>0.7536</v>
       </c>
       <c r="N64" t="n">
-        <v>0.1272</v>
+        <v>0.1744</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>1561.1</v>
+        <v>1637.4</v>
       </c>
       <c r="Q64" t="n">
         <v>10805</v>
@@ -9372,7 +9372,7 @@
         <v>0.9193</v>
       </c>
       <c r="G65" t="n">
-        <v>0.996</v>
+        <v>0.9954</v>
       </c>
       <c r="H65" t="n">
         <v>0.3125</v>
@@ -9381,25 +9381,25 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L65" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M65" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.7638</v>
       </c>
       <c r="N65" t="n">
-        <v>0.1128</v>
+        <v>0.1386</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>1406.9</v>
+        <v>1635.6</v>
       </c>
       <c r="Q65" t="n">
         <v>11954</v>
@@ -9429,7 +9429,7 @@
         <v>0.9098000000000001</v>
       </c>
       <c r="G66" t="n">
-        <v>0.9937</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="H66" t="n">
         <v>0.5625</v>
@@ -9438,25 +9438,25 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K66" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L66" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M66" t="n">
-        <v>0.8197</v>
+        <v>0.8228</v>
       </c>
       <c r="N66" t="n">
-        <v>0.1565</v>
+        <v>0.1628</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>1426.4</v>
+        <v>1231.2</v>
       </c>
       <c r="Q66" t="n">
         <v>8299</v>
@@ -9486,7 +9486,7 @@
         <v>0.9466</v>
       </c>
       <c r="G67" t="n">
-        <v>0.9948</v>
+        <v>0.9978</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -9495,25 +9495,25 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K67" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L67" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M67" t="n">
-        <v>0.6952</v>
+        <v>0.7007</v>
       </c>
       <c r="N67" t="n">
-        <v>0.1234</v>
+        <v>0.1022</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>1606.8</v>
+        <v>672.1</v>
       </c>
       <c r="Q67" t="n">
         <v>10391</v>
@@ -9543,7 +9543,7 @@
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>0.9933999999999999</v>
+        <v>0.9976</v>
       </c>
       <c r="H68" t="n">
         <v>0.625</v>
@@ -9552,25 +9552,25 @@
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K68" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L68" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M68" t="n">
-        <v>0.8996</v>
+        <v>0.9014</v>
       </c>
       <c r="N68" t="n">
-        <v>0.2085</v>
+        <v>0.1013</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>1232.4</v>
+        <v>443.9</v>
       </c>
       <c r="Q68" t="n">
         <v>4966</v>
@@ -9600,7 +9600,7 @@
         <v>0.9353</v>
       </c>
       <c r="G69" t="n">
-        <v>0.997</v>
+        <v>0.9973</v>
       </c>
       <c r="H69" t="n">
         <v>0.6875</v>
@@ -9609,25 +9609,25 @@
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K69" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L69" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M69" t="n">
-        <v>0.8711</v>
+        <v>0.8733</v>
       </c>
       <c r="N69" t="n">
-        <v>0.1199</v>
+        <v>0.0759</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>762.4</v>
+        <v>678.5</v>
       </c>
       <c r="Q69" t="n">
         <v>6437</v>
@@ -9657,7 +9657,7 @@
         <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>0.994</v>
+        <v>0.9989</v>
       </c>
       <c r="H70" t="n">
         <v>0.1562</v>
@@ -9666,25 +9666,25 @@
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K70" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L70" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M70" t="n">
-        <v>0.7743</v>
+        <v>0.7785</v>
       </c>
       <c r="N70" t="n">
-        <v>0.1552</v>
+        <v>0.0324</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>908.2</v>
+        <v>165.7</v>
       </c>
       <c r="Q70" t="n">
         <v>4414</v>
@@ -9714,7 +9714,7 @@
         <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>0.9965000000000001</v>
+        <v>0.9997</v>
       </c>
       <c r="H71" t="n">
         <v>0.09370000000000001</v>
@@ -9723,25 +9723,25 @@
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>0.7005</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K71" t="n">
-        <v>0.0322</v>
+        <v>0.0495</v>
       </c>
       <c r="L71" t="n">
-        <v>0.2673</v>
+        <v>0.2625</v>
       </c>
       <c r="M71" t="n">
-        <v>0.7577</v>
+        <v>0.7621</v>
       </c>
       <c r="N71" t="n">
-        <v>0.1056</v>
+        <v>0.005</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>715.4</v>
+        <v>55.1</v>
       </c>
       <c r="Q71" t="n">
         <v>5931</v>
@@ -9771,7 +9771,7 @@
         <v>0.9203</v>
       </c>
       <c r="G72" t="n">
-        <v>0.9942</v>
+        <v>0.9947</v>
       </c>
       <c r="H72" t="n">
         <v>0.875</v>
@@ -9780,25 +9780,25 @@
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>0.6016</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K72" t="n">
-        <v>0.1689</v>
+        <v>0.0495</v>
       </c>
       <c r="L72" t="n">
-        <v>0.2295</v>
+        <v>0.2625</v>
       </c>
       <c r="M72" t="n">
-        <v>0.9224</v>
+        <v>0.9121</v>
       </c>
       <c r="N72" t="n">
-        <v>0.1295</v>
+        <v>0.1803</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>1883.9</v>
+        <v>1709.9</v>
       </c>
       <c r="Q72" t="n">
         <v>13885</v>
@@ -9828,7 +9828,7 @@
         <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>0.988</v>
+        <v>0.9941</v>
       </c>
       <c r="H73" t="n">
         <v>0.8125</v>
@@ -9837,25 +9837,25 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>0.6016</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K73" t="n">
-        <v>0.1689</v>
+        <v>0.0495</v>
       </c>
       <c r="L73" t="n">
-        <v>0.2295</v>
+        <v>0.2625</v>
       </c>
       <c r="M73" t="n">
-        <v>0.9549</v>
+        <v>0.9505</v>
       </c>
       <c r="N73" t="n">
-        <v>0.132</v>
+        <v>0.1811</v>
       </c>
       <c r="O73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>2125.2</v>
+        <v>1748.7</v>
       </c>
       <c r="Q73" t="n">
         <v>12828</v>
@@ -9885,7 +9885,7 @@
         <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>0.9932</v>
+        <v>0.9929</v>
       </c>
       <c r="H74" t="n">
         <v>0.0625</v>
@@ -9894,25 +9894,25 @@
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>0.6016</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K74" t="n">
-        <v>0.1689</v>
+        <v>0.0495</v>
       </c>
       <c r="L74" t="n">
-        <v>0.2295</v>
+        <v>0.2625</v>
       </c>
       <c r="M74" t="n">
-        <v>0.7837</v>
+        <v>0.7536</v>
       </c>
       <c r="N74" t="n">
-        <v>0.1526</v>
+        <v>0.2092</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>1873.3</v>
+        <v>1964.9</v>
       </c>
       <c r="Q74" t="n">
         <v>10805</v>
@@ -9942,7 +9942,7 @@
         <v>0.9193</v>
       </c>
       <c r="G75" t="n">
-        <v>0.9952</v>
+        <v>0.9944</v>
       </c>
       <c r="H75" t="n">
         <v>0.3125</v>
@@ -9951,25 +9951,25 @@
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>0.6016</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K75" t="n">
-        <v>0.1689</v>
+        <v>0.0495</v>
       </c>
       <c r="L75" t="n">
-        <v>0.2295</v>
+        <v>0.2625</v>
       </c>
       <c r="M75" t="n">
-        <v>0.7927999999999999</v>
+        <v>0.7637</v>
       </c>
       <c r="N75" t="n">
-        <v>0.1354</v>
+        <v>0.1663</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>1688.3</v>
+        <v>1962.7</v>
       </c>
       <c r="Q75" t="n">
         <v>11954</v>
@@ -9999,7 +9999,7 @@
         <v>0.9098000000000001</v>
       </c>
       <c r="G76" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.9933999999999999</v>
       </c>
       <c r="H76" t="n">
         <v>0.5625</v>
@@ -10008,25 +10008,25 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>0.6016</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K76" t="n">
-        <v>0.1689</v>
+        <v>0.0495</v>
       </c>
       <c r="L76" t="n">
-        <v>0.2295</v>
+        <v>0.2625</v>
       </c>
       <c r="M76" t="n">
-        <v>0.844</v>
+        <v>0.8228</v>
       </c>
       <c r="N76" t="n">
-        <v>0.1878</v>
+        <v>0.1953</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>1711.7</v>
+        <v>1477.4</v>
       </c>
       <c r="Q76" t="n">
         <v>8299</v>
@@ -10056,7 +10056,7 @@
         <v>0.9466</v>
       </c>
       <c r="G77" t="n">
-        <v>0.9937</v>
+        <v>0.9974</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -10065,25 +10065,25 @@
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>0.6016</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>0.1689</v>
+        <v>0.0495</v>
       </c>
       <c r="L77" t="n">
-        <v>0.2295</v>
+        <v>0.2625</v>
       </c>
       <c r="M77" t="n">
-        <v>0.7373</v>
+        <v>0.7006</v>
       </c>
       <c r="N77" t="n">
-        <v>0.1481</v>
+        <v>0.1227</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>1928.2</v>
+        <v>806.5</v>
       </c>
       <c r="Q77" t="n">
         <v>10391</v>
@@ -10113,7 +10113,7 @@
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>0.992</v>
+        <v>0.9971</v>
       </c>
       <c r="H78" t="n">
         <v>0.625</v>
@@ -10122,25 +10122,25 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>0.6016</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>0.1689</v>
+        <v>0.0495</v>
       </c>
       <c r="L78" t="n">
-        <v>0.2295</v>
+        <v>0.2625</v>
       </c>
       <c r="M78" t="n">
-        <v>0.9126</v>
+        <v>0.9014</v>
       </c>
       <c r="N78" t="n">
-        <v>0.2502</v>
+        <v>0.1215</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>1478.8</v>
+        <v>532.7</v>
       </c>
       <c r="Q78" t="n">
         <v>4966</v>
@@ -10170,7 +10170,7 @@
         <v>0.9353</v>
       </c>
       <c r="G79" t="n">
-        <v>0.9964</v>
+        <v>0.9968</v>
       </c>
       <c r="H79" t="n">
         <v>0.6875</v>
@@ -10179,25 +10179,25 @@
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>0.6016</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K79" t="n">
-        <v>0.1689</v>
+        <v>0.0495</v>
       </c>
       <c r="L79" t="n">
-        <v>0.2295</v>
+        <v>0.2625</v>
       </c>
       <c r="M79" t="n">
-        <v>0.8887</v>
+        <v>0.8733</v>
       </c>
       <c r="N79" t="n">
-        <v>0.1439</v>
+        <v>0.091</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>914.8</v>
+        <v>814.2</v>
       </c>
       <c r="Q79" t="n">
         <v>6437</v>
@@ -10227,7 +10227,7 @@
         <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>0.9928</v>
+        <v>0.9987</v>
       </c>
       <c r="H80" t="n">
         <v>0.1562</v>
@@ -10236,25 +10236,25 @@
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>0.6016</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K80" t="n">
-        <v>0.1689</v>
+        <v>0.0495</v>
       </c>
       <c r="L80" t="n">
-        <v>0.2295</v>
+        <v>0.2625</v>
       </c>
       <c r="M80" t="n">
-        <v>0.8051</v>
+        <v>0.7784</v>
       </c>
       <c r="N80" t="n">
-        <v>0.1862</v>
+        <v>0.0389</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>1089.9</v>
+        <v>198.9</v>
       </c>
       <c r="Q80" t="n">
         <v>4414</v>
@@ -10284,7 +10284,7 @@
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>0.9958</v>
+        <v>0.9997</v>
       </c>
       <c r="H81" t="n">
         <v>0.09370000000000001</v>
@@ -10293,25 +10293,25 @@
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>0.6016</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K81" t="n">
-        <v>0.1689</v>
+        <v>0.0495</v>
       </c>
       <c r="L81" t="n">
-        <v>0.2295</v>
+        <v>0.2625</v>
       </c>
       <c r="M81" t="n">
-        <v>0.7913</v>
+        <v>0.7621</v>
       </c>
       <c r="N81" t="n">
-        <v>0.1267</v>
+        <v>0.006</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>858.5</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="Q81" t="n">
         <v>5931</v>
@@ -10341,7 +10341,7 @@
         <v>0.9203</v>
       </c>
       <c r="G82" t="n">
-        <v>0.9235</v>
+        <v>0.9937</v>
       </c>
       <c r="H82" t="n">
         <v>0.875</v>
@@ -10350,25 +10350,25 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>0.4257</v>
+        <v>0.3101</v>
       </c>
       <c r="K82" t="n">
-        <v>0.5281</v>
+        <v>0.5715</v>
       </c>
       <c r="L82" t="n">
-        <v>0.0462</v>
+        <v>0.1183</v>
       </c>
       <c r="M82" t="n">
-        <v>0.9199000000000001</v>
+        <v>0.9569</v>
       </c>
       <c r="N82" t="n">
-        <v>0.1554</v>
+        <v>0.2164</v>
       </c>
       <c r="O82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>2260.7</v>
+        <v>2051.9</v>
       </c>
       <c r="Q82" t="n">
         <v>13885</v>
@@ -10398,37 +10398,37 @@
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>0.7856</v>
+        <v>0.993</v>
       </c>
       <c r="H83" t="n">
-        <v>0.3438</v>
+        <v>0.8125</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>0.4257</v>
+        <v>0.3101</v>
       </c>
       <c r="K83" t="n">
-        <v>0.5281</v>
+        <v>0.5715</v>
       </c>
       <c r="L83" t="n">
-        <v>0.0462</v>
+        <v>0.1183</v>
       </c>
       <c r="M83" t="n">
-        <v>0.8565</v>
+        <v>0.9738</v>
       </c>
       <c r="N83" t="n">
-        <v>0.1572</v>
+        <v>0.2173</v>
       </c>
       <c r="O83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>2550.2</v>
+        <v>2098.5</v>
       </c>
       <c r="Q83" t="n">
-        <v>12920</v>
+        <v>12828</v>
       </c>
     </row>
     <row r="84">
@@ -10455,7 +10455,7 @@
         <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>0.9296</v>
+        <v>0.8772</v>
       </c>
       <c r="H84" t="n">
         <v>0.0625</v>
@@ -10464,25 +10464,25 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>0.4257</v>
+        <v>0.3101</v>
       </c>
       <c r="K84" t="n">
-        <v>0.5281</v>
+        <v>0.5715</v>
       </c>
       <c r="L84" t="n">
-        <v>0.0462</v>
+        <v>0.1183</v>
       </c>
       <c r="M84" t="n">
-        <v>0.9195</v>
+        <v>0.8189</v>
       </c>
       <c r="N84" t="n">
-        <v>0.1831</v>
+        <v>0.2511</v>
       </c>
       <c r="O84" t="n">
         <v>1</v>
       </c>
       <c r="P84" t="n">
-        <v>2247.9</v>
+        <v>2357.9</v>
       </c>
       <c r="Q84" t="n">
         <v>10805</v>
@@ -10512,7 +10512,7 @@
         <v>0.9193</v>
       </c>
       <c r="G85" t="n">
-        <v>0.9942</v>
+        <v>0.8784</v>
       </c>
       <c r="H85" t="n">
         <v>0.3125</v>
@@ -10521,25 +10521,25 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>0.4257</v>
+        <v>0.3101</v>
       </c>
       <c r="K85" t="n">
-        <v>0.5281</v>
+        <v>0.5715</v>
       </c>
       <c r="L85" t="n">
-        <v>0.0462</v>
+        <v>0.1183</v>
       </c>
       <c r="M85" t="n">
-        <v>0.9308</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="N85" t="n">
-        <v>0.1625</v>
+        <v>0.1996</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P85" t="n">
-        <v>2026</v>
+        <v>2355.3</v>
       </c>
       <c r="Q85" t="n">
         <v>11954</v>
@@ -10569,7 +10569,7 @@
         <v>0.9098000000000001</v>
       </c>
       <c r="G86" t="n">
-        <v>0.9909</v>
+        <v>0.9921</v>
       </c>
       <c r="H86" t="n">
         <v>0.5625</v>
@@ -10578,25 +10578,25 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>0.4257</v>
+        <v>0.3101</v>
       </c>
       <c r="K86" t="n">
-        <v>0.5281</v>
+        <v>0.5715</v>
       </c>
       <c r="L86" t="n">
-        <v>0.0462</v>
+        <v>0.1183</v>
       </c>
       <c r="M86" t="n">
-        <v>0.9366</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="N86" t="n">
-        <v>0.2253</v>
+        <v>0.2344</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>2054.1</v>
+        <v>1772.9</v>
       </c>
       <c r="Q86" t="n">
         <v>8299</v>
@@ -10626,7 +10626,7 @@
         <v>0.9466</v>
       </c>
       <c r="G87" t="n">
-        <v>0.8982</v>
+        <v>0.9969</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -10635,25 +10635,25 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>0.4257</v>
+        <v>0.3101</v>
       </c>
       <c r="K87" t="n">
-        <v>0.5281</v>
+        <v>0.5715</v>
       </c>
       <c r="L87" t="n">
-        <v>0.0462</v>
+        <v>0.1183</v>
       </c>
       <c r="M87" t="n">
-        <v>0.8773</v>
+        <v>0.8633</v>
       </c>
       <c r="N87" t="n">
-        <v>0.1778</v>
+        <v>0.1472</v>
       </c>
       <c r="O87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>2313.8</v>
+        <v>967.8</v>
       </c>
       <c r="Q87" t="n">
         <v>10391</v>
@@ -10683,7 +10683,7 @@
         <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>0.9905</v>
+        <v>0.9966</v>
       </c>
       <c r="H88" t="n">
         <v>0.625</v>
@@ -10692,25 +10692,25 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>0.4257</v>
+        <v>0.3101</v>
       </c>
       <c r="K88" t="n">
-        <v>0.5281</v>
+        <v>0.5715</v>
       </c>
       <c r="L88" t="n">
-        <v>0.0462</v>
+        <v>0.1183</v>
       </c>
       <c r="M88" t="n">
-        <v>0.9776</v>
+        <v>0.9537</v>
       </c>
       <c r="N88" t="n">
-        <v>0.3003</v>
+        <v>0.1458</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>1774.6</v>
+        <v>639.2</v>
       </c>
       <c r="Q88" t="n">
         <v>4966</v>
@@ -10740,7 +10740,7 @@
         <v>0.9353</v>
       </c>
       <c r="G89" t="n">
-        <v>0.9957</v>
+        <v>0.9962</v>
       </c>
       <c r="H89" t="n">
         <v>0.6875</v>
@@ -10749,25 +10749,25 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>0.4257</v>
+        <v>0.3101</v>
       </c>
       <c r="K89" t="n">
-        <v>0.5281</v>
+        <v>0.5715</v>
       </c>
       <c r="L89" t="n">
-        <v>0.0462</v>
+        <v>0.1183</v>
       </c>
       <c r="M89" t="n">
-        <v>0.9557</v>
+        <v>0.9408</v>
       </c>
       <c r="N89" t="n">
-        <v>0.1727</v>
+        <v>0.1093</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>1097.8</v>
+        <v>977</v>
       </c>
       <c r="Q89" t="n">
         <v>6437</v>
@@ -10797,7 +10797,7 @@
         <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>0.9913999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="H90" t="n">
         <v>0.1562</v>
@@ -10806,25 +10806,25 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>0.4257</v>
+        <v>0.3101</v>
       </c>
       <c r="K90" t="n">
-        <v>0.5281</v>
+        <v>0.5715</v>
       </c>
       <c r="L90" t="n">
-        <v>0.0462</v>
+        <v>0.1183</v>
       </c>
       <c r="M90" t="n">
-        <v>0.9565</v>
+        <v>0.8993</v>
       </c>
       <c r="N90" t="n">
-        <v>0.2235</v>
+        <v>0.0467</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>1307.9</v>
+        <v>238.7</v>
       </c>
       <c r="Q90" t="n">
         <v>4414</v>
@@ -10854,7 +10854,7 @@
         <v>1</v>
       </c>
       <c r="G91" t="n">
-        <v>0.995</v>
+        <v>0.9996</v>
       </c>
       <c r="H91" t="n">
         <v>0.09370000000000001</v>
@@ -10863,25 +10863,25 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>0.4257</v>
+        <v>0.3101</v>
       </c>
       <c r="K91" t="n">
-        <v>0.5281</v>
+        <v>0.5715</v>
       </c>
       <c r="L91" t="n">
-        <v>0.0462</v>
+        <v>0.1183</v>
       </c>
       <c r="M91" t="n">
-        <v>0.9555</v>
+        <v>0.8925</v>
       </c>
       <c r="N91" t="n">
-        <v>0.1521</v>
+        <v>0.0072</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>1030.2</v>
+        <v>79.3</v>
       </c>
       <c r="Q91" t="n">
         <v>5931</v>
@@ -10950,7 +10950,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C2" t="n">
         <v>6</v>
@@ -10961,10 +10961,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.6952</v>
+        <v>0.7006</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1234</v>
+        <v>0.1227</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -10972,7 +10972,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.4095</v>
+        <v>0.4065</v>
       </c>
     </row>
     <row r="3">
@@ -10985,18 +10985,18 @@
         <v>2027</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>新城街道</t>
+          <t>凤凰山街道</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.7373</v>
+        <v>0.7536</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1481</v>
+        <v>0.2092</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.3958</v>
+        <v>0.406</v>
       </c>
     </row>
     <row r="4">
@@ -11017,18 +11017,18 @@
         <v>2026</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>凤凰山街道</t>
+          <t>新城街道</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.7493</v>
+        <v>0.7007</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1272</v>
+        <v>0.1022</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -11036,7 +11036,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.3835</v>
+        <v>0.4003</v>
       </c>
     </row>
     <row r="5">
@@ -11049,18 +11049,18 @@
         <v>2026</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>凤凰山街道</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.7743</v>
+        <v>0.7536</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1552</v>
+        <v>0.1744</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -11068,7 +11068,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.3794</v>
+        <v>0.3955</v>
       </c>
     </row>
     <row r="6">
@@ -11078,7 +11078,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
@@ -11089,10 +11089,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.7637</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1128</v>
+        <v>0.1663</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -11100,7 +11100,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.374</v>
+        <v>0.388</v>
       </c>
     </row>
     <row r="7">
@@ -11110,7 +11110,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C7" t="n">
         <v>3</v>
@@ -11121,10 +11121,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.7837</v>
+        <v>0.8189</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1526</v>
+        <v>0.2511</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.3739</v>
+        <v>0.3859</v>
       </c>
     </row>
     <row r="8">
@@ -11142,21 +11142,21 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.8051</v>
+        <v>0.7638</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1862</v>
+        <v>0.1386</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.3733</v>
+        <v>0.3797</v>
       </c>
     </row>
     <row r="9">
@@ -11174,21 +11174,21 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.7577</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1056</v>
+        <v>0.1996</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.3728</v>
+        <v>0.3678</v>
       </c>
     </row>
     <row r="10">
@@ -11209,18 +11209,18 @@
         <v>2027</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.7927999999999999</v>
+        <v>0.8228</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1354</v>
+        <v>0.1953</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.3642</v>
+        <v>0.3672</v>
       </c>
     </row>
     <row r="11">
@@ -11238,21 +11238,21 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.7913</v>
+        <v>0.8228</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1267</v>
+        <v>0.1628</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -11260,39 +11260,39 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.3624</v>
+        <v>0.3574</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>新城街道</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.8197</v>
+        <v>0.7006</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1565</v>
+        <v>0.1176</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.3571</v>
+        <v>0.3462</v>
       </c>
     </row>
     <row r="13">
@@ -11305,18 +11305,18 @@
         <v>2027</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>新城街道</t>
+          <t>凤凰山街道</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.6951000000000001</v>
+        <v>0.7536</v>
       </c>
       <c r="F13" t="n">
-        <v>0.142</v>
+        <v>0.2005</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.3563</v>
+        <v>0.3446</v>
       </c>
     </row>
     <row r="14">
@@ -11337,18 +11337,18 @@
         <v>2027</v>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>姚店镇</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.844</v>
+        <v>0.7784</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1878</v>
+        <v>0.0389</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.3543</v>
+        <v>0.3425</v>
       </c>
     </row>
     <row r="15">
@@ -11377,10 +11377,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.6952</v>
+        <v>0.7007</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1234</v>
+        <v>0.1022</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -11388,7 +11388,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.3507</v>
+        <v>0.3416</v>
       </c>
     </row>
     <row r="16">
@@ -11398,21 +11398,21 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>南市街道</t>
+          <t>李渠镇</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.8565</v>
+        <v>0.7621</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1572</v>
+        <v>0.006</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -11420,7 +11420,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.3389</v>
+        <v>0.3407</v>
       </c>
     </row>
     <row r="17">
@@ -11430,21 +11430,21 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>姚店镇</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9126</v>
+        <v>0.7785</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2502</v>
+        <v>0.0324</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.3388</v>
+        <v>0.3405</v>
       </c>
     </row>
     <row r="18">
@@ -11462,21 +11462,21 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>新城街道</t>
+          <t>李渠镇</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.8773</v>
+        <v>0.7621</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1778</v>
+        <v>0.005</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -11484,103 +11484,103 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.3347</v>
+        <v>0.3404</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2026</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>凤凰山街道</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.8996</v>
+        <v>0.7536</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2085</v>
+        <v>0.1744</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.3328</v>
+        <v>0.3368</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>凤凰山街道</t>
+          <t>新城街道</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.7492</v>
+        <v>0.8633</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1462</v>
+        <v>0.1472</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.3305</v>
+        <v>0.3325</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C21" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.7743</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1785</v>
+        <v>0.2344</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.3277</v>
+        <v>0.3324</v>
       </c>
     </row>
     <row r="22">
@@ -11590,21 +11590,21 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>凤凰山街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.7493</v>
+        <v>0.7637</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1272</v>
+        <v>0.1594</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -11612,103 +11612,103 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0.3248</v>
+        <v>0.3272</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.9776</v>
+        <v>0.7638</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3003</v>
+        <v>0.1386</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.3213</v>
+        <v>0.3209</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C24" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>宝塔山街道</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.7743</v>
+        <v>0.9121</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1552</v>
+        <v>0.1803</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.3207</v>
+        <v>0.318</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>2027</v>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.8733</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1297</v>
+        <v>0.091</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0.3204</v>
+        <v>0.3107</v>
       </c>
     </row>
     <row r="26">
@@ -11721,18 +11721,18 @@
         <v>2026</v>
       </c>
       <c r="C26" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>宝塔山街道</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.8711</v>
+        <v>0.9121</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1199</v>
+        <v>0.1503</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0.3204</v>
+        <v>0.309</v>
       </c>
     </row>
     <row r="27">
@@ -11753,18 +11753,18 @@
         <v>2028</v>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>宝塔山街道</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.9366</v>
+        <v>0.9569</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2253</v>
+        <v>0.2164</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -11772,7 +11772,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.3193</v>
+        <v>0.3065</v>
       </c>
     </row>
     <row r="28">
@@ -11782,21 +11782,21 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C28" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>凤凰山街道</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.7577</v>
+        <v>0.8487</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1215</v>
+        <v>0.2306</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0.3189</v>
+        <v>0.3061</v>
       </c>
     </row>
     <row r="29">
@@ -11814,7 +11814,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C29" t="n">
         <v>8</v>
@@ -11825,10 +11825,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.8887</v>
+        <v>0.8733</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1439</v>
+        <v>0.0759</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -11836,7 +11836,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.3188</v>
+        <v>0.3061</v>
       </c>
     </row>
     <row r="30">
@@ -11846,21 +11846,21 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.8228</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1128</v>
+        <v>0.1872</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0.3153</v>
+        <v>0.306</v>
       </c>
     </row>
     <row r="31">
@@ -11878,21 +11878,21 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>凤凰山街道</t>
+          <t>柳林镇</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.9195</v>
+        <v>0.9014</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1831</v>
+        <v>0.1215</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -11900,39 +11900,39 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0.3152</v>
+        <v>0.3057</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>2026</v>
       </c>
       <c r="C32" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>柳林镇</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.7577</v>
+        <v>0.9014</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1056</v>
+        <v>0.1013</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.3141</v>
+        <v>0.2997</v>
       </c>
     </row>
     <row r="33">
@@ -11942,21 +11942,21 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C33" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>南市街道</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.9565</v>
+        <v>0.9505</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2235</v>
+        <v>0.1811</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -11964,359 +11964,359 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0.3088</v>
+        <v>0.2991</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>宝塔山街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9199000000000001</v>
+        <v>0.8228</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1554</v>
+        <v>0.1628</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0.3067</v>
+        <v>0.2987</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C35" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>南市街道</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.8197</v>
+        <v>0.9738</v>
       </c>
       <c r="F35" t="n">
-        <v>0.1799</v>
+        <v>0.2173</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0.3054</v>
+        <v>0.2983</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>2028</v>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>新城街道</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.9308</v>
+        <v>0.7006</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1625</v>
+        <v>0.1237</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0.3033</v>
+        <v>0.2918</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>凤凰山街道</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.8197</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>0.1565</v>
+        <v>0.211</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0.2983</v>
+        <v>0.2915</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>新城街道</t>
+          <t>南市街道</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.6951000000000001</v>
+        <v>0.9505</v>
       </c>
       <c r="F38" t="n">
-        <v>0.1358</v>
+        <v>0.1509</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0.2982</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>宝塔山街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.9224</v>
+        <v>0.8548</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1295</v>
+        <v>0.1833</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0.2977</v>
+        <v>0.2888</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>宝塔山街道</t>
+          <t>新城街道</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.9106</v>
+        <v>0.7006</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1079</v>
+        <v>0.1125</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0.2971</v>
+        <v>0.2884</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C41" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>新城街道</t>
+          <t>柳林镇</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.6952</v>
+        <v>0.9537</v>
       </c>
       <c r="F41" t="n">
-        <v>0.1234</v>
+        <v>0.1458</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0.2945</v>
+        <v>0.2869</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C42" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>凤凰山街道</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.9557</v>
+        <v>0.7536</v>
       </c>
       <c r="F42" t="n">
-        <v>0.1727</v>
+        <v>0.1918</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0.2939</v>
+        <v>0.2857</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>2028</v>
       </c>
       <c r="C43" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>新城街道</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.9555</v>
+        <v>0.8325</v>
       </c>
       <c r="F43" t="n">
-        <v>0.1521</v>
+        <v>0.1352</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0.2879</v>
+        <v>0.2856</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C44" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>新城街道</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.8995</v>
+        <v>0.7007</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2398</v>
+        <v>0.1022</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0.2834</v>
+        <v>0.2853</v>
       </c>
     </row>
     <row r="45">
@@ -12326,21 +12326,21 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>南市街道</t>
+          <t>姚店镇</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.9549</v>
+        <v>0.8993</v>
       </c>
       <c r="F45" t="n">
-        <v>0.132</v>
+        <v>0.0467</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.2821</v>
+        <v>0.2844</v>
       </c>
     </row>
     <row r="46">
@@ -12358,21 +12358,21 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>新城街道</t>
+          <t>姚店镇</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.8595</v>
+        <v>0.7785</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1633</v>
+        <v>0.0373</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.2805</v>
+        <v>0.2832</v>
       </c>
     </row>
     <row r="47">
@@ -12390,21 +12390,21 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>南市街道</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.9497</v>
+        <v>0.9408</v>
       </c>
       <c r="F47" t="n">
-        <v>0.11</v>
+        <v>0.1093</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -12412,7 +12412,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0.2781</v>
+        <v>0.2824</v>
       </c>
     </row>
     <row r="48">
@@ -12422,21 +12422,21 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>李渠镇</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.8966</v>
+        <v>0.7621</v>
       </c>
       <c r="F48" t="n">
-        <v>0.2052</v>
+        <v>0.0057</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0.2745</v>
+        <v>0.2819</v>
       </c>
     </row>
     <row r="49">
@@ -12457,18 +12457,18 @@
         <v>2026</v>
       </c>
       <c r="C49" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>姚店镇</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.8996</v>
+        <v>0.7785</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2085</v>
+        <v>0.0324</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -12476,39 +12476,39 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.274</v>
+        <v>0.2818</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>凤凰山街道</t>
+          <t>李渠镇</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.7492</v>
+        <v>0.7621</v>
       </c>
       <c r="F50" t="n">
-        <v>0.1399</v>
+        <v>0.005</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0.2723</v>
+        <v>0.2817</v>
       </c>
     </row>
     <row r="51">
@@ -12518,21 +12518,21 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C51" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>凤凰山街道</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.7743</v>
+        <v>0.7536</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1707</v>
+        <v>0.1744</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>0.2691</v>
+        <v>0.2805</v>
       </c>
     </row>
     <row r="52">
@@ -12553,18 +12553,18 @@
         <v>2028</v>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>凤凰山街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.8858</v>
+        <v>0.8984</v>
       </c>
       <c r="F52" t="n">
-        <v>0.1682</v>
+        <v>0.2152</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -12572,167 +12572,167 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0.2688</v>
+        <v>0.2766</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>凤凰山街道</t>
+          <t>李渠镇</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.7493</v>
+        <v>0.8925</v>
       </c>
       <c r="F53" t="n">
-        <v>0.1272</v>
+        <v>0.0072</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.2685</v>
+        <v>0.2759</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>2028</v>
       </c>
       <c r="C54" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.951</v>
+        <v>0.7637</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2758</v>
+        <v>0.1677</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>0.2685</v>
+        <v>0.2734</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>2027</v>
       </c>
       <c r="C55" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.871</v>
+        <v>0.7638</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1379</v>
+        <v>0.1524</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.2671</v>
+        <v>0.2689</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.9162</v>
+        <v>0.7638</v>
       </c>
       <c r="F56" t="n">
-        <v>0.2069</v>
+        <v>0.1386</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.2652</v>
+        <v>0.2647</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C57" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>宝塔山街道</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.7743</v>
+        <v>0.9121</v>
       </c>
       <c r="F57" t="n">
-        <v>0.1552</v>
+        <v>0.1728</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>0.2644</v>
+        <v>0.257</v>
       </c>
     </row>
     <row r="58">
@@ -12742,21 +12742,21 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.8228</v>
       </c>
       <c r="F58" t="n">
-        <v>0.1241</v>
+        <v>0.1969</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -12764,7 +12764,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>0.2624</v>
+        <v>0.2527</v>
       </c>
     </row>
     <row r="59">
@@ -12774,7 +12774,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C59" t="n">
         <v>8</v>
@@ -12785,10 +12785,10 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.8711</v>
+        <v>0.8733</v>
       </c>
       <c r="F59" t="n">
-        <v>0.1199</v>
+        <v>0.0873</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -12796,39 +12796,39 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>0.2617</v>
+        <v>0.2508</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C60" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>宝塔山街道</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.7577</v>
+        <v>0.9121</v>
       </c>
       <c r="F60" t="n">
-        <v>0.1162</v>
+        <v>0.1503</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>0.261</v>
+        <v>0.2503</v>
       </c>
     </row>
     <row r="61">
@@ -12838,21 +12838,21 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C61" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.8915999999999999</v>
+        <v>0.8733</v>
       </c>
       <c r="F61" t="n">
-        <v>0.1492</v>
+        <v>0.0759</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0.2602</v>
+        <v>0.2474</v>
       </c>
     </row>
     <row r="62">
@@ -12870,21 +12870,21 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.8228</v>
       </c>
       <c r="F62" t="n">
-        <v>0.1128</v>
+        <v>0.179</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -12892,39 +12892,39 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>0.259</v>
+        <v>0.2473</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C63" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>宝塔山街道</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.7577</v>
+        <v>0.9486</v>
       </c>
       <c r="F63" t="n">
-        <v>0.1056</v>
+        <v>0.1987</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>0.2578</v>
+        <v>0.2466</v>
       </c>
     </row>
     <row r="64">
@@ -12934,21 +12934,21 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C64" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>柳林镇</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.8911</v>
+        <v>0.9014</v>
       </c>
       <c r="F64" t="n">
-        <v>0.1397</v>
+        <v>0.1164</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -12956,71 +12956,71 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>0.2576</v>
+        <v>0.2455</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>南市街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.9117</v>
+        <v>0.8228</v>
       </c>
       <c r="F65" t="n">
-        <v>0.1454</v>
+        <v>0.1628</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>0.249</v>
+        <v>0.2424</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C66" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>柳林镇</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.8197</v>
+        <v>0.9014</v>
       </c>
       <c r="F66" t="n">
-        <v>0.1721</v>
+        <v>0.1013</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>0.2468</v>
+        <v>0.2409</v>
       </c>
     </row>
     <row r="67">
@@ -13033,18 +13033,18 @@
         <v>2027</v>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>宝塔山街道</t>
+          <t>南市街道</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.9106</v>
+        <v>0.9505</v>
       </c>
       <c r="F67" t="n">
-        <v>0.1241</v>
+        <v>0.1736</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -13052,71 +13052,71 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>0.2432</v>
+        <v>0.2381</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C68" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>南市街道</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.8197</v>
+        <v>0.9696</v>
       </c>
       <c r="F68" t="n">
-        <v>0.1565</v>
+        <v>0.1996</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>0.2421</v>
+        <v>0.2363</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>2028</v>
       </c>
       <c r="C69" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>新城街道</t>
+          <t>姚店镇</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.8174</v>
+        <v>0.8764</v>
       </c>
       <c r="F69" t="n">
-        <v>0.1494</v>
+        <v>0.0429</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>0.2411</v>
+        <v>0.2359</v>
       </c>
     </row>
     <row r="70">
@@ -13129,18 +13129,18 @@
         <v>2026</v>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>宝塔山街道</t>
+          <t>南市街道</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.9106</v>
+        <v>0.9505</v>
       </c>
       <c r="F70" t="n">
-        <v>0.1079</v>
+        <v>0.1509</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -13148,7 +13148,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>0.2383</v>
+        <v>0.2313</v>
       </c>
     </row>
     <row r="71">
@@ -13161,18 +13161,18 @@
         <v>2028</v>
       </c>
       <c r="C71" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>柳林镇</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.9412</v>
+        <v>0.9439</v>
       </c>
       <c r="F71" t="n">
-        <v>0.1586</v>
+        <v>0.1339</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -13180,39 +13180,39 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>0.2382</v>
+        <v>0.2295</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B72" t="n">
         <v>2028</v>
       </c>
       <c r="C72" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>李渠镇</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.8637</v>
+        <v>0.8678</v>
       </c>
       <c r="F72" t="n">
-        <v>0.1878</v>
+        <v>0.0066</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>0.2295</v>
+        <v>0.2293</v>
       </c>
     </row>
     <row r="73">
@@ -13225,18 +13225,18 @@
         <v>2028</v>
       </c>
       <c r="C73" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>凤凰山街道</t>
+          <t>姚店镇</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.8491</v>
+        <v>0.7784</v>
       </c>
       <c r="F73" t="n">
-        <v>0.1539</v>
+        <v>0.0393</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>0.2266</v>
+        <v>0.2276</v>
       </c>
     </row>
     <row r="74">
@@ -13257,18 +13257,18 @@
         <v>2028</v>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>宝塔山街道</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.9572000000000001</v>
+        <v>0.9281</v>
       </c>
       <c r="F74" t="n">
-        <v>0.1427</v>
+        <v>0.1003</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -13276,39 +13276,39 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>0.2255</v>
+        <v>0.2273</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>2027</v>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>南市街道</t>
+          <t>姚店镇</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.9497</v>
+        <v>0.7785</v>
       </c>
       <c r="F75" t="n">
-        <v>0.1265</v>
+        <v>0.0357</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>0.2244</v>
+        <v>0.2265</v>
       </c>
     </row>
     <row r="76">
@@ -13318,21 +13318,21 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C76" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>李渠镇</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.8995</v>
+        <v>0.7621</v>
       </c>
       <c r="F76" t="n">
-        <v>0.2294</v>
+        <v>0.006</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -13340,39 +13340,39 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>0.224</v>
+        <v>0.2258</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>南市街道</t>
+          <t>李渠镇</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.9497</v>
+        <v>0.7621</v>
       </c>
       <c r="F77" t="n">
-        <v>0.11</v>
+        <v>0.0055</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>0.2194</v>
+        <v>0.2256</v>
       </c>
     </row>
     <row r="78">
@@ -13382,21 +13382,21 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C78" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>姚店镇</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.856</v>
+        <v>0.7785</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1365</v>
+        <v>0.0324</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>0.2179</v>
+        <v>0.2255</v>
       </c>
     </row>
     <row r="79">
@@ -13417,18 +13417,18 @@
         <v>2026</v>
       </c>
       <c r="C79" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>李渠镇</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.8996</v>
+        <v>0.7621</v>
       </c>
       <c r="F79" t="n">
-        <v>0.2085</v>
+        <v>0.005</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -13436,7 +13436,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>0.2178</v>
+        <v>0.2254</v>
       </c>
     </row>
     <row r="80">
@@ -13449,18 +13449,18 @@
         <v>2028</v>
       </c>
       <c r="C80" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>宝塔山街道</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.8903</v>
+        <v>0.9121</v>
       </c>
       <c r="F80" t="n">
-        <v>0.1893</v>
+        <v>0.1818</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>0.2166</v>
+        <v>0.2035</v>
       </c>
     </row>
     <row r="81">
@@ -13478,21 +13478,21 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C81" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>宝塔山街道</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.8551</v>
+        <v>0.9121</v>
       </c>
       <c r="F81" t="n">
-        <v>0.1278</v>
+        <v>0.1653</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>0.2158</v>
+        <v>0.1985</v>
       </c>
     </row>
     <row r="82">
@@ -13513,18 +13513,18 @@
         <v>2028</v>
       </c>
       <c r="C82" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.9374</v>
+        <v>0.8733</v>
       </c>
       <c r="F82" t="n">
-        <v>0.2523</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>0.212</v>
+        <v>0.1959</v>
       </c>
     </row>
     <row r="83">
@@ -13542,21 +13542,21 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C83" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>宝塔山街道</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.8711</v>
+        <v>0.9121</v>
       </c>
       <c r="F83" t="n">
-        <v>0.1319</v>
+        <v>0.1503</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -13564,7 +13564,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>0.209</v>
+        <v>0.194</v>
       </c>
     </row>
     <row r="84">
@@ -13574,7 +13574,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C84" t="n">
         <v>8</v>
@@ -13585,10 +13585,10 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.8711</v>
+        <v>0.8733</v>
       </c>
       <c r="F84" t="n">
-        <v>0.1199</v>
+        <v>0.0835</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -13596,7 +13596,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>0.2054</v>
+        <v>0.1934</v>
       </c>
     </row>
     <row r="85">
@@ -13606,7 +13606,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C85" t="n">
         <v>8</v>
@@ -13617,10 +13617,10 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.9224</v>
+        <v>0.8733</v>
       </c>
       <c r="F85" t="n">
-        <v>0.1451</v>
+        <v>0.0759</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -13628,7 +13628,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>0.1873</v>
+        <v>0.1911</v>
       </c>
     </row>
     <row r="86">
@@ -13638,21 +13638,21 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>宝塔山街道</t>
+          <t>柳林镇</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.9106</v>
+        <v>0.9014</v>
       </c>
       <c r="F86" t="n">
-        <v>0.1187</v>
+        <v>0.1225</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>0.1853</v>
+        <v>0.191</v>
       </c>
     </row>
     <row r="87">
@@ -13670,21 +13670,21 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>宝塔山街道</t>
+          <t>柳林镇</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.9106</v>
+        <v>0.9014</v>
       </c>
       <c r="F87" t="n">
-        <v>0.1079</v>
+        <v>0.1114</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>0.1821</v>
+        <v>0.1877</v>
       </c>
     </row>
     <row r="88">
@@ -13702,21 +13702,21 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>宝塔山街道</t>
+          <t>柳林镇</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.9448</v>
+        <v>0.9014</v>
       </c>
       <c r="F88" t="n">
-        <v>0.1306</v>
+        <v>0.1013</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -13724,7 +13724,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>0.1718</v>
+        <v>0.1847</v>
       </c>
     </row>
     <row r="89">
@@ -13734,7 +13734,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C89" t="n">
         <v>2</v>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.9497</v>
+        <v>0.9505</v>
       </c>
       <c r="F89" t="n">
-        <v>0.121</v>
+        <v>0.1826</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -13756,7 +13756,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>0.1664</v>
+        <v>0.1845</v>
       </c>
     </row>
     <row r="90">
@@ -13766,7 +13766,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C90" t="n">
         <v>2</v>
@@ -13777,10 +13777,10 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.9617</v>
+        <v>0.9505</v>
       </c>
       <c r="F90" t="n">
-        <v>0.1331</v>
+        <v>0.166</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -13788,7 +13788,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>0.1641</v>
+        <v>0.1796</v>
       </c>
     </row>
     <row r="91">
@@ -13809,10 +13809,10 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.9497</v>
+        <v>0.9505</v>
       </c>
       <c r="F91" t="n">
-        <v>0.11</v>
+        <v>0.1509</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>0.1631</v>
+        <v>0.175</v>
       </c>
     </row>
   </sheetData>
@@ -13834,7 +13834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13892,25 +13892,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2028</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>南市街道</t>
+          <t>凤凰山街道</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.9617</v>
+        <v>0.8487</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1331</v>
+        <v>0.2306</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -13937,27 +13937,27 @@
         <v>2028</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>南市街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.9117</v>
+        <v>0.8548</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1454</v>
+        <v>0.1833</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -13968,34 +13968,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>2028</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>新城街道</t>
+          <t>凤凰山街道</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.8595</v>
+        <v>0.8189</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1633</v>
+        <v>0.2511</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -14010,184 +14010,32 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>南市街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.9549</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>0.132</v>
+        <v>0.1996</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J5" t="inlineStr">
-        <is>
-          <t>过载分流</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>高增长(20%)</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2028</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>宝塔山街道</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>0.9199000000000001</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.1554</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>12</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>过载分流</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>高增长(20%)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2028</v>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>南市街道</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0.8565</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.1572</v>
-      </c>
-      <c r="G7" t="n">
-        <v>5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>30</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>过载分流</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>高增长(20%)</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2028</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>凤凰山街道</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>0.9195</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.1831</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>12</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>过载分流</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>高增长(20%)</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2028</v>
-      </c>
-      <c r="C9" t="n">
-        <v>6</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>新城街道</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0.8773</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.1778</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>18</v>
-      </c>
-      <c r="J9" t="inlineStr">
         <is>
           <t>过载分流</t>
         </is>
@@ -14256,19 +14104,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>164.5</v>
+        <v>161.8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8898</v>
+        <v>0.8218</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -14283,16 +14131,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>179.8</v>
+        <v>176.8</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9102</v>
+        <v>0.8969</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
@@ -14310,19 +14158,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>195.8</v>
+        <v>192.5</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9286</v>
+        <v>0.9039</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
